--- a/data/СВОДНАЯ.xlsx
+++ b/data/СВОДНАЯ.xlsx
@@ -1,25 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\izrantsevavs\Desktop\Рабочая\кибер турнир\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\izrantsevavs\Desktop\Рабочая\кибер турнир\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D2AB128-0CF5-480E-8CB5-DB129CA93CE5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C7429E6-ABB5-4FE5-BE92-2534801D561B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26850" windowHeight="12555" xr2:uid="{67E04C49-DBAE-4188-9035-2652F6F89765}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" activeTab="4" xr2:uid="{67E04C49-DBAE-4188-9035-2652F6F89765}"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
-    <sheet name="Справочник" sheetId="2" r:id="rId2"/>
+    <sheet name="сводная" sheetId="1" r:id="rId1"/>
+    <sheet name="профсоюз" sheetId="4" r:id="rId2"/>
+    <sheet name="Участники" sheetId="3" r:id="rId3"/>
+    <sheet name="таблица 2" sheetId="8" r:id="rId4"/>
+    <sheet name="Расписание 9-21" sheetId="7" r:id="rId5"/>
+    <sheet name="Расписание 9-20" sheetId="9" state="hidden" r:id="rId6"/>
+    <sheet name="Расписание (короткое)" sheetId="5" state="hidden" r:id="rId7"/>
+    <sheet name="Справочник" sheetId="2" r:id="rId8"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId9"/>
+    <externalReference r:id="rId10"/>
+    <externalReference r:id="rId11"/>
+  </externalReferences>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">сводная!$B$2:$O$50</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -31,7 +48,7 @@
     <author>Попов Владислав Владимирович</author>
   </authors>
   <commentList>
-    <comment ref="G11" authorId="0" shapeId="0" xr:uid="{B408B825-D48D-440F-8CAB-E2057DAA21AD}">
+    <comment ref="G8" authorId="0" shapeId="0" xr:uid="{B408B825-D48D-440F-8CAB-E2057DAA21AD}">
       <text>
         <r>
           <rPr>
@@ -62,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="386">
   <si>
     <t>Ник</t>
   </si>
@@ -199,77 +216,1048 @@
     <t>Исаев Дамир Эдуардович</t>
   </si>
   <si>
+    <t>Шайнога Богдан Тарасович</t>
+  </si>
+  <si>
+    <t>Шестаков Дмитрий Игоревич</t>
+  </si>
+  <si>
+    <t>dim0590</t>
+  </si>
+  <si>
+    <t>Dmitry.Shestakov@lukoil.com</t>
+  </si>
+  <si>
+    <t>8-905-440-21-70</t>
+  </si>
+  <si>
+    <t>Destro</t>
+  </si>
+  <si>
+    <t>Destro#5565</t>
+  </si>
+  <si>
+    <t>Damir.Isaev@lukoil.com</t>
+  </si>
+  <si>
+    <t>8-960-855-79-19</t>
+  </si>
+  <si>
+    <t>p_irozhok#7781</t>
+  </si>
+  <si>
+    <t>Попов Владислав Владимирович</t>
+  </si>
+  <si>
+    <t>Nate_HHIgers_808</t>
+  </si>
+  <si>
+    <t>нет</t>
+  </si>
+  <si>
+    <t>ищу команду, готов быть в лоутабе</t>
+  </si>
+  <si>
+    <t>vladislav.v.popov@lukoil.com</t>
+  </si>
+  <si>
+    <t>8-961-666-78-08</t>
+  </si>
+  <si>
+    <t>Хасянов Марат Алиевич</t>
+  </si>
+  <si>
+    <t>xm777</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>ищу команду</t>
+  </si>
+  <si>
+    <t>xm777@ya.ru</t>
+  </si>
+  <si>
+    <t>Чепендюк Евгений</t>
+  </si>
+  <si>
+    <t>Babah</t>
+  </si>
+  <si>
+    <t>evgeny.chependyuk@lukoil.com</t>
+  </si>
+  <si>
+    <t>8-916-711-56-21</t>
+  </si>
+  <si>
+    <t>Козловский Дмитрий Сергеевич</t>
+  </si>
+  <si>
+    <t>Мужчина Эталон</t>
+  </si>
+  <si>
+    <t>Волгоград (дистанционно)</t>
+  </si>
+  <si>
+    <t>sqwoz_dust</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Волгоград, участие дистанционно</t>
+  </si>
+  <si>
+    <t>Dmitry.Kozlovsky@lukoil.com</t>
+  </si>
+  <si>
+    <t>Есауленко Александр Александрович</t>
+  </si>
+  <si>
+    <t>I`m you</t>
+  </si>
+  <si>
+    <t>Волгоград, участие дистанционно</t>
+  </si>
+  <si>
+    <t>Aleksandr.Esaulenko@lukoil.com</t>
+  </si>
+  <si>
+    <t>Седойкин Андрей Александрович</t>
+  </si>
+  <si>
+    <t>Fee-Fi-Fo-Fum</t>
+  </si>
+  <si>
+    <t>andrey.sedoykin@lukoil.com</t>
+  </si>
+  <si>
+    <t>Комиссаров Дмитирий Сергеевич</t>
+  </si>
+  <si>
+    <t>Harley</t>
+  </si>
+  <si>
+    <t>dmitriy.s.komissarov@lukoil.com</t>
+  </si>
+  <si>
+    <t>Кузнецов Александр Петрович</t>
+  </si>
+  <si>
+    <t>Riesling</t>
+  </si>
+  <si>
+    <t>+</t>
+  </si>
+  <si>
+    <t>aleksandr.p.kuznetsov@lukoil.com</t>
+  </si>
+  <si>
+    <t>Локутов Артур Владленович</t>
+  </si>
+  <si>
+    <t>Artur.Lokutov@lukoil.com</t>
+  </si>
+  <si>
+    <t>8-968-822-06-26</t>
+  </si>
+  <si>
+    <t>Антонов Артем Александрович</t>
+  </si>
+  <si>
+    <t>Artem.Antonov@lukoil.com</t>
+  </si>
+  <si>
+    <t>8-916-258-36-22</t>
+  </si>
+  <si>
+    <t>Малахов Никита Андреевич</t>
+  </si>
+  <si>
+    <t>Nikita.Malakhov@lukoil.com</t>
+  </si>
+  <si>
+    <t>8-916-712-55-35</t>
+  </si>
+  <si>
+    <t>Саитов Аскар Альбертович</t>
+  </si>
+  <si>
+    <t>Askar.Saitov@lukoil.com</t>
+  </si>
+  <si>
+    <t>8-985-413-23-11</t>
+  </si>
+  <si>
+    <t>Балабушко Константин Яковлевич</t>
+  </si>
+  <si>
+    <t>Konstantin.Balabushko@lukoil.com</t>
+  </si>
+  <si>
+    <t>8-925-275-58-94</t>
+  </si>
+  <si>
+    <t>Овчинников Илья Игоревич</t>
+  </si>
+  <si>
+    <t>off4eg</t>
+  </si>
+  <si>
+    <t>ilya.ovchinnikov@lukoil.com</t>
+  </si>
+  <si>
+    <t>8-919-469-76-73</t>
+  </si>
+  <si>
+    <t>Карпов Александр Андреевич</t>
+  </si>
+  <si>
+    <t>Snoopy</t>
+  </si>
+  <si>
+    <t>DarklingMean38#5987</t>
+  </si>
+  <si>
+    <t>Широлапики</t>
+  </si>
+  <si>
+    <t>------------</t>
+  </si>
+  <si>
+    <t>sashka20020118@gmail.com</t>
+  </si>
+  <si>
+    <t>8-915-111-27-51</t>
+  </si>
+  <si>
+    <t>Самохвалов Михаил Сергеевич</t>
+  </si>
+  <si>
+    <t>Ra's Al Ghul</t>
+  </si>
+  <si>
+    <t>Rasalghul#5359</t>
+  </si>
+  <si>
+    <t>Misha557777@gmail.com</t>
+  </si>
+  <si>
+    <t>8-961-087-01-51</t>
+  </si>
+  <si>
+    <t>Земляных Матвей Валерьевич</t>
+  </si>
+  <si>
+    <t>death</t>
+  </si>
+  <si>
+    <t>Matvey.Zemlyanykh@lukoil.com</t>
+  </si>
+  <si>
+    <t>(08495)32807</t>
+  </si>
+  <si>
+    <t>Мешков Кирилл Андреевич</t>
+  </si>
+  <si>
+    <t>F4rtun4</t>
+  </si>
+  <si>
+    <t>f4rtun4</t>
+  </si>
+  <si>
+    <t>Kirill.Meshkov@lukoil.com</t>
+  </si>
+  <si>
+    <t>8-985-600-97-71</t>
+  </si>
+  <si>
+    <t>Шейчук Яков Иванович</t>
+  </si>
+  <si>
+    <t>LavaYasha</t>
+  </si>
+  <si>
+    <t>yakov7636</t>
+  </si>
+  <si>
+    <t>yakovsheychuk@gmail.com</t>
+  </si>
+  <si>
+    <t>8-985-437-72-76</t>
+  </si>
+  <si>
+    <t>Скиндар Альбина Геннадьевна</t>
+  </si>
+  <si>
+    <t>Boormazyaka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">у капитана </t>
+  </si>
+  <si>
+    <t>Oil Ghoulz</t>
+  </si>
+  <si>
+    <t>Albina.Skindar@lukoil.com</t>
+  </si>
+  <si>
+    <t>(08495) 58719</t>
+  </si>
+  <si>
+    <t>Головин Антон Анатольевич</t>
+  </si>
+  <si>
+    <t>Buchyo</t>
+  </si>
+  <si>
+    <t>Anton.Golovin@lukoil.com</t>
+  </si>
+  <si>
+    <t>(08495) 68557</t>
+  </si>
+  <si>
+    <t>Зырянов Артем Вячеславович</t>
+  </si>
+  <si>
+    <t>eror404</t>
+  </si>
+  <si>
+    <t>Artem.Zyryanov@lukoil.com</t>
+  </si>
+  <si>
+    <t>нету</t>
+  </si>
+  <si>
+    <t>Кострикин Егор Алексеевич</t>
+  </si>
+  <si>
+    <t>artig</t>
+  </si>
+  <si>
+    <t>Egor.Kostrikin@lukoil.com</t>
+  </si>
+  <si>
+    <t>(08342) 58205</t>
+  </si>
+  <si>
+    <t>Витулев Владислав Алексеевич</t>
+  </si>
+  <si>
+    <t>PravoSLavik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 игрок запасной </t>
+  </si>
+  <si>
+    <t>Vladislav.Vitulev@lukoil.com</t>
+  </si>
+  <si>
+    <t>Кульпин Сергей Витальевич</t>
+  </si>
+  <si>
+    <t>entercl4p</t>
+  </si>
+  <si>
+    <t>Да</t>
+  </si>
+  <si>
+    <t>LukTechPrime</t>
+  </si>
+  <si>
+    <t>Sergey.Kulpin@lukoil.com</t>
+  </si>
+  <si>
+    <t>Ярославцев Егор Викторович</t>
+  </si>
+  <si>
+    <t>EgorNachos</t>
+  </si>
+  <si>
+    <t>Egor.Yaroslavtsev@lukoil.com</t>
+  </si>
+  <si>
+    <t>Михайлов Дмитрий Николаевич</t>
+  </si>
+  <si>
+    <t>fntz</t>
+  </si>
+  <si>
+    <t>Dmitry.Mikhaylov@lukoil.com</t>
+  </si>
+  <si>
+    <t>Шабронов Алексей Сергеевич</t>
+  </si>
+  <si>
+    <t>loremear</t>
+  </si>
+  <si>
+    <t>Aleksey.Shabronov@lukoil.com</t>
+  </si>
+  <si>
+    <t>Савенок Николай Николаевич</t>
+  </si>
+  <si>
+    <t>L4H4L</t>
+  </si>
+  <si>
+    <t>Nikolay.Savenok@lukoil.com</t>
+  </si>
+  <si>
+    <t>Тепляков Кирилл Евгеньевич</t>
+  </si>
+  <si>
+    <t>tepl</t>
+  </si>
+  <si>
+    <t>76561198342101914</t>
+  </si>
+  <si>
+    <t>CSPerm</t>
+  </si>
+  <si>
+    <t>^^</t>
+  </si>
+  <si>
+    <t>Kirill.Teplyakov@lukoil.com</t>
+  </si>
+  <si>
+    <t>Полынский Арсений Андреевич</t>
+  </si>
+  <si>
+    <t>G.Raptor</t>
+  </si>
+  <si>
+    <t>76561199209149559</t>
+  </si>
+  <si>
+    <t>Arseniy.Polynsky@lukoil.com</t>
+  </si>
+  <si>
+    <t>89194869117</t>
+  </si>
+  <si>
+    <t>Габов Артемий Александрович</t>
+  </si>
+  <si>
+    <t>76561199745282573</t>
+  </si>
+  <si>
+    <t>gab0v</t>
+  </si>
+  <si>
+    <t>artemy.gabov@lukoil.com</t>
+  </si>
+  <si>
+    <t>89526600567</t>
+  </si>
+  <si>
+    <t>Куликов Максим Юрьевич</t>
+  </si>
+  <si>
+    <t>_GG_</t>
+  </si>
+  <si>
+    <t>76561199535374304</t>
+  </si>
+  <si>
+    <t>Max_Kul</t>
+  </si>
+  <si>
+    <t>Maxim.Kulikov@lukoil.com</t>
+  </si>
+  <si>
+    <t>89197166473</t>
+  </si>
+  <si>
+    <t>Галинов Олег Юрьевич</t>
+  </si>
+  <si>
+    <t>:)</t>
+  </si>
+  <si>
+    <t>76561199113997400</t>
+  </si>
+  <si>
+    <t>galileg</t>
+  </si>
+  <si>
+    <t>Oleg.Galinov@lukoil.com</t>
+  </si>
+  <si>
+    <t>89222410186</t>
+  </si>
+  <si>
+    <t>Садилов Александр Дмитриевич</t>
+  </si>
+  <si>
+    <t xml:space="preserve">beznachos </t>
+  </si>
+  <si>
+    <t>76561198325726847</t>
+  </si>
+  <si>
+    <t>bisnachaus</t>
+  </si>
+  <si>
+    <t>Alexandr.Sadilov@lukoil.com</t>
+  </si>
+  <si>
+    <t>89323376753</t>
+  </si>
+  <si>
+    <t>Неталиев Адиль Аманович;</t>
+  </si>
+  <si>
+    <t>Гуров Илья Николаевич;</t>
+  </si>
+  <si>
+    <t>Ярцев Семен Александрович;</t>
+  </si>
+  <si>
+    <t>Плетнев Никита Дмитриевич</t>
+  </si>
+  <si>
+    <t>Тойватров Владимир Юрьевич</t>
+  </si>
+  <si>
+    <t>1+B4:N47</t>
+  </si>
+  <si>
+    <t>Наконечный Роман Константинович</t>
+  </si>
+  <si>
+    <t>NRK</t>
+  </si>
+  <si>
+    <t>это 1.6…</t>
+  </si>
+  <si>
+    <t>---</t>
+  </si>
+  <si>
+    <t>профессиональный игрок в компьютер</t>
+  </si>
+  <si>
+    <t>Roman.Nakonechnyy@lukoil.com</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>№</t>
+  </si>
+  <si>
+    <t>Участники</t>
+  </si>
+  <si>
+    <t>Статус игрока (дистанционно/очно)</t>
+  </si>
+  <si>
+    <t>Команда 1</t>
+  </si>
+  <si>
+    <t>CS 1.6</t>
+  </si>
+  <si>
+    <t>Очно</t>
+  </si>
+  <si>
+    <t>Команда 2</t>
+  </si>
+  <si>
+    <t>CS2</t>
+  </si>
+  <si>
+    <t>Dota 2</t>
+  </si>
+  <si>
+    <t>Неталиев Адиль Аманович</t>
+  </si>
+  <si>
     <t>Гуров Илья Николаевич</t>
   </si>
   <si>
-    <t>Шайнога Богдан Тарасович</t>
-  </si>
-  <si>
-    <t>Неталиев Адиль Аманович</t>
-  </si>
-  <si>
-    <t>FREY</t>
-  </si>
-  <si>
-    <t>Шестаков Дмитрий Игоревич</t>
-  </si>
-  <si>
-    <t>dim0590</t>
-  </si>
-  <si>
-    <t>Dmitry.Shestakov@lukoil.com</t>
-  </si>
-  <si>
-    <t>8-905-440-21-70</t>
-  </si>
-  <si>
-    <t>Destro</t>
-  </si>
-  <si>
-    <t>Perezagruzka</t>
-  </si>
-  <si>
-    <t>Destro#5565</t>
-  </si>
-  <si>
-    <t>Damir.Isaev@lukoil.com</t>
-  </si>
-  <si>
-    <t>8-960-855-79-19</t>
-  </si>
-  <si>
-    <t>p_irozhok#7781</t>
-  </si>
-  <si>
-    <t>Попов Владислав Владимирович</t>
-  </si>
-  <si>
-    <t>Nate_HHIgers_808</t>
-  </si>
-  <si>
-    <t>нет</t>
-  </si>
-  <si>
-    <t>ищу команду, готов быть в лоутабе</t>
-  </si>
-  <si>
-    <t>vladislav.v.popov@lukoil.com</t>
-  </si>
-  <si>
-    <t>8-961-666-78-08</t>
+    <t>Ярцев Семен Александрович</t>
+  </si>
+  <si>
+    <t>Пермяков Никита Андреевич</t>
+  </si>
+  <si>
+    <t>Рожков Кирилл Владимирович</t>
+  </si>
+  <si>
+    <t>Kirill.Rozhkov@lukoil.com</t>
+  </si>
+  <si>
+    <t>Givenchy</t>
+  </si>
+  <si>
+    <t>egor.tarakanchikov@lukoil.com</t>
+  </si>
+  <si>
+    <t>8-902-906-06-37</t>
+  </si>
+  <si>
+    <t>Тараканчиков Егор Сергеевич</t>
+  </si>
+  <si>
+    <t>есть (egorushka_life)</t>
+  </si>
+  <si>
+    <t>буду медиком с рпг</t>
+  </si>
+  <si>
+    <t>Состоит в Профсоюзе</t>
+  </si>
+  <si>
+    <t>Изранцева Виктория Сергеевна</t>
+  </si>
+  <si>
+    <t>дамир</t>
+  </si>
+  <si>
+    <t>09:00 – 10:00</t>
+  </si>
+  <si>
+    <t>60 мин</t>
+  </si>
+  <si>
+    <t>10:00 – 10:30</t>
+  </si>
+  <si>
+    <t>30 мин</t>
+  </si>
+  <si>
+    <t>10:30 - 11:30</t>
+  </si>
+  <si>
+    <t>CS2: Матч 1 (1/4)</t>
+  </si>
+  <si>
+    <t>Dota 2: Финал (Матч 1)</t>
+  </si>
+  <si>
+    <t>1 час</t>
+  </si>
+  <si>
+    <t>Обеденный перерыв, свободное время</t>
+  </si>
+  <si>
+    <t>30 минут</t>
+  </si>
+  <si>
+    <t>12:30 - 13:30</t>
+  </si>
+  <si>
+    <t>Dota 2: Финал (Матч 2)</t>
+  </si>
+  <si>
+    <t>CS2: Матч 1 (1/2)</t>
+  </si>
+  <si>
+    <t>14:00 - 15:00</t>
+  </si>
+  <si>
+    <t>CS2: Матч 1 (финал)</t>
+  </si>
+  <si>
+    <t>CS2: Матч 2 (1/2)</t>
+  </si>
+  <si>
+    <t>CS2: Матч 1 (III место)</t>
+  </si>
+  <si>
+    <t>Dota 2: Финал (Матч 3) (опционально)</t>
+  </si>
+  <si>
+    <t>13:30 - 14:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIFA </t>
+  </si>
+  <si>
+    <t>3 плойки</t>
+  </si>
+  <si>
+    <t>1 час 30 мин</t>
+  </si>
+  <si>
+    <t>16:00 - 17:00</t>
+  </si>
+  <si>
+    <t>13:00 - 14:00</t>
+  </si>
+  <si>
+    <t>14:30 - 15:30</t>
+  </si>
+  <si>
+    <t>15:30 - 16:00</t>
+  </si>
+  <si>
+    <t>11:30 - 12:00</t>
+  </si>
+  <si>
+    <t>12:00 - 13:00</t>
+  </si>
+  <si>
+    <t>12:00 - 12:30</t>
+  </si>
+  <si>
+    <t>14:30 - 15:00</t>
+  </si>
+  <si>
+    <t>Шоу-матч</t>
+  </si>
+  <si>
+    <t>Награждение</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Регистрация </t>
+  </si>
+  <si>
+    <t>Официальное открытие</t>
+  </si>
+  <si>
+    <t>Закрытие кибертурнира</t>
+  </si>
+  <si>
+    <t>CS2: Матч 1 (1 - 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 час </t>
+  </si>
+  <si>
+    <t>CS2: Матч 1 (3 - 4)</t>
+  </si>
+  <si>
+    <t>CS2: Матч 1 (1 - 3)</t>
+  </si>
+  <si>
+    <t>CS2: Матч 1 (2 - 5)</t>
+  </si>
+  <si>
+    <t>CS2: Матч 1 (1 - 4)</t>
+  </si>
+  <si>
+    <t>CS2: Матч 1 (3 - 5)</t>
+  </si>
+  <si>
+    <t>CS2: Матч 1 (1 - 5)</t>
+  </si>
+  <si>
+    <t>CS2: Матч 1 (2 - 4)</t>
+  </si>
+  <si>
+    <t>17:00 - 17:30</t>
+  </si>
+  <si>
+    <t>17:30 - 18:30</t>
+  </si>
+  <si>
+    <t>CS2: Матч 1 (2 - 3)</t>
+  </si>
+  <si>
+    <t>CS2: Матч 1 (4 - 5)</t>
+  </si>
+  <si>
+    <t>21:00 – 21:30</t>
+  </si>
+  <si>
+    <t>11:30 - 13:00</t>
+  </si>
+  <si>
+    <t>CS 1.6 (опционально)</t>
+  </si>
+  <si>
+    <t>20:30 – 21:00</t>
+  </si>
+  <si>
+    <t>2 часа</t>
+  </si>
+  <si>
+    <t>18:30 - 20:30</t>
+  </si>
+  <si>
+    <t>17:00 - 19:00</t>
+  </si>
+  <si>
+    <t>19:00 – 19:30</t>
+  </si>
+  <si>
+    <t>19:30 – 20:00</t>
+  </si>
+  <si>
+    <t>Мероприятие</t>
+  </si>
+  <si>
+    <t>Кто играет</t>
+  </si>
+  <si>
+    <t>Регистрация</t>
+  </si>
+  <si>
+    <t>Открытие</t>
+  </si>
+  <si>
+    <t>Dota 2: Матч 1</t>
+  </si>
+  <si>
+    <t>Ком. 1 vs 2</t>
+  </si>
+  <si>
+    <t>Dota 2: Матч 2</t>
+  </si>
+  <si>
+    <t>Dota 2: Матч 3</t>
+  </si>
+  <si>
+    <t>CS2: Матч 1</t>
+  </si>
+  <si>
+    <t>CS2: Матч 2</t>
+  </si>
+  <si>
+    <t>Ком. 3 vs 4</t>
+  </si>
+  <si>
+    <t>CS2: Матч 3</t>
+  </si>
+  <si>
+    <t>Ком. 1 vs 3</t>
+  </si>
+  <si>
+    <t>CS2: Матч 4</t>
+  </si>
+  <si>
+    <t>Ком. 2 vs 5</t>
+  </si>
+  <si>
+    <t>CS2: Матч 5</t>
+  </si>
+  <si>
+    <t>Ком. 1 vs 4</t>
+  </si>
+  <si>
+    <t>CS2: Матч 6</t>
+  </si>
+  <si>
+    <t>Ком. 3 vs 5</t>
+  </si>
+  <si>
+    <t>CS2: Матч 7</t>
+  </si>
+  <si>
+    <t>Ком. 1 vs 5</t>
+  </si>
+  <si>
+    <t>CS2: Матч 8</t>
+  </si>
+  <si>
+    <t>Ком. 2 vs 4</t>
+  </si>
+  <si>
+    <t>CS2: Матч 9</t>
+  </si>
+  <si>
+    <t>Ком. 2 vs 3</t>
+  </si>
+  <si>
+    <t>CS2: Матч 10</t>
+  </si>
+  <si>
+    <t>Ком. 4 vs 5</t>
+  </si>
+  <si>
+    <t>FIFA: Турнир</t>
+  </si>
+  <si>
+    <t>5 уч.</t>
+  </si>
+  <si>
+    <t>MK: Турнир</t>
+  </si>
+  <si>
+    <t>6 уч.</t>
+  </si>
+  <si>
+    <t>CS 1.6: Шоу-матч</t>
+  </si>
+  <si>
+    <t>2 команды</t>
+  </si>
+  <si>
+    <t>Все</t>
+  </si>
+  <si>
+    <t>Обед</t>
+  </si>
+  <si>
+    <t>Закрытие</t>
+  </si>
+  <si>
+    <t>4 плойки</t>
+  </si>
+  <si>
+    <t>Dota 2: Финал (Матч 1-3)</t>
+  </si>
+  <si>
+    <t>10:30 - 12:30</t>
+  </si>
+  <si>
+    <t>11:30 - 13:30</t>
+  </si>
+  <si>
+    <t>CS 1.6: Финал (Матч 1-3)</t>
+  </si>
+  <si>
+    <t>11:30 - 12:30</t>
+  </si>
+  <si>
+    <t>13:30 - 14:00</t>
+  </si>
+  <si>
+    <t>15:00 - 15:30</t>
+  </si>
+  <si>
+    <t>15:30 - 16:30</t>
+  </si>
+  <si>
+    <t>16:30 - 17:30</t>
+  </si>
+  <si>
+    <t>45 мин</t>
+  </si>
+  <si>
+    <t>10:30 - 11:15</t>
+  </si>
+  <si>
+    <t>11:15 - 12:00</t>
+  </si>
+  <si>
+    <t>12:00 - 12:45</t>
+  </si>
+  <si>
+    <t>15:30 - 16:15</t>
+  </si>
+  <si>
+    <t>16:15 - 17:00</t>
+  </si>
+  <si>
+    <t>16:15 - 17:15</t>
+  </si>
+  <si>
+    <t>17:15 - 19:15</t>
+  </si>
+  <si>
+    <t>19:15 – 19:45</t>
+  </si>
+  <si>
+    <t>19:45 – 20:15</t>
+  </si>
+  <si>
+    <t>Сбор участников, официальное открытие</t>
+  </si>
+  <si>
+    <t>17:30 – 18:00</t>
+  </si>
+  <si>
+    <t>Награждение, закрытие кибертурнира</t>
+  </si>
+  <si>
+    <t>Тараканчиков</t>
+  </si>
+  <si>
+    <t>Опционально</t>
+  </si>
+  <si>
+    <t>CS 1.6: Матч 1</t>
+  </si>
+  <si>
+    <t>CS 1.6:: Матч 2</t>
+  </si>
+  <si>
+    <t>CS 1.6:: Матч 3</t>
+  </si>
+  <si>
+    <t>Название</t>
+  </si>
+  <si>
+    <t>Васина В.</t>
+  </si>
+  <si>
+    <t>Изранцева В.</t>
+  </si>
+  <si>
+    <t>Шайнога Б.</t>
+  </si>
+  <si>
+    <t>Гуров И.</t>
+  </si>
+  <si>
+    <t>Исаев Д.</t>
+  </si>
+  <si>
+    <t>Хасянов М.</t>
+  </si>
+  <si>
+    <t>Чепендюк Е.</t>
+  </si>
+  <si>
+    <t>Папичев Н.</t>
+  </si>
+  <si>
+    <t>Шестаков Д.</t>
+  </si>
+  <si>
+    <t>Овчинников И.</t>
+  </si>
+  <si>
+    <t>Неталиев А.</t>
+  </si>
+  <si>
+    <t>Команда 3</t>
+  </si>
+  <si>
+    <t>Команда 5</t>
+  </si>
+  <si>
+    <t>Команда 4</t>
+  </si>
+  <si>
+    <t>Victory</t>
+  </si>
+  <si>
+    <t>10:30 - 12:00</t>
+  </si>
+  <si>
+    <t>15 мин</t>
+  </si>
+  <si>
+    <t>10:00 – 10:15</t>
+  </si>
+  <si>
+    <t>13:00 - 13:30</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="2"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -319,8 +1307,59 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -345,8 +1384,110 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED7D31"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD92DE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF99FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="40">
     <border>
       <left/>
       <right/>
@@ -398,16 +1539,336 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -417,23 +1878,19 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
+      <top/>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -444,7 +1901,44 @@
         <color indexed="64"/>
       </right>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -456,46 +1950,14 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
+      <top/>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -506,102 +1968,493 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="31" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="31" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный 2" xfId="2" xr:uid="{BD2F2D3F-5147-4381-BE8E-6AE9FE7F7167}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFBD92DE"/>
+      <color rgb="FFFF99FF"/>
+      <color rgb="FFCCCCFF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -611,6 +2464,47 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Справочник"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Справочник"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Лист1"/>
+      <sheetName val="Справочник"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -910,13 +2804,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF88F6F3-0D6A-4594-A26D-5FF47BF11826}">
-  <dimension ref="B1:O11"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:O59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.140625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.28515625" style="2" customWidth="1"/>
     <col min="2" max="2" width="30.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.140625" style="26" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.5703125" style="2" customWidth="1"/>
     <col min="6" max="6" width="27.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.85546875" style="2" bestFit="1" customWidth="1"/>
@@ -930,333 +2827,362 @@
     <col min="15" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" s="1" customFormat="1" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:15" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="12" t="s">
+    <row r="1" spans="1:15" s="1" customFormat="1" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D1" s="22"/>
+    </row>
+    <row r="2" spans="1:15" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="29" t="s">
+        <v>220</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="J2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="K2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="12" t="s">
+      <c r="L2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="M2" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="N2" s="13" t="s">
+      <c r="N2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="O2" s="14" t="s">
+      <c r="O2" s="7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" s="10" t="s">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="N3" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="O3" s="11" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>14</v>
+      <c r="J3" s="16">
+        <v>1</v>
+      </c>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>24</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>16</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="J4" s="16">
+        <v>1</v>
+      </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
-      <c r="M4" s="10" t="s">
-        <v>38</v>
+      <c r="M4" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O4" s="11" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5" s="3">
-        <v>1146157829</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>58</v>
-      </c>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>25</v>
+      <c r="G5" s="17" t="s">
+        <v>24</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>16</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="21"/>
+        <v>20</v>
+      </c>
+      <c r="J5" s="16">
+        <v>1</v>
+      </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
-      <c r="M5" s="10" t="s">
-        <v>42</v>
+      <c r="M5" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="O5" s="20"/>
-    </row>
-    <row r="6" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="3">
-        <v>368217808</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>55</v>
-      </c>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>25</v>
+      <c r="G6" s="17" t="s">
+        <v>24</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>16</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="22"/>
+        <v>20</v>
+      </c>
+      <c r="J6" s="16">
+        <v>1</v>
+      </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
-      <c r="M6" s="17" t="s">
-        <v>56</v>
+      <c r="M6" s="3" t="s">
+        <v>100</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="O6" s="20"/>
-    </row>
-    <row r="7" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D7" s="3"/>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="24"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>25</v>
+      <c r="G7" s="17" t="s">
+        <v>24</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>16</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" s="22"/>
+        <v>20</v>
+      </c>
+      <c r="J7" s="16">
+        <v>1</v>
+      </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="20"/>
-    </row>
-    <row r="8" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
+      <c r="M7" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="24"/>
+      <c r="E8" s="3" t="s">
+        <v>57</v>
+      </c>
       <c r="F8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>25</v>
+        <v>11</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>24</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>16</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J8" s="23"/>
+        <v>20</v>
+      </c>
+      <c r="J8" s="3"/>
       <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="20"/>
-    </row>
-    <row r="9" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="7" t="s">
-        <v>47</v>
+      <c r="L8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
+        <v>62</v>
+      </c>
+      <c r="D9" s="24"/>
+      <c r="E9" s="3" t="s">
+        <v>63</v>
+      </c>
       <c r="F9" s="3"/>
-      <c r="G9" s="3" t="s">
-        <v>26</v>
+      <c r="G9" s="17" t="s">
+        <v>24</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>16</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="8"/>
-    </row>
-    <row r="10" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="7" t="s">
-        <v>49</v>
+      <c r="L9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="N9" s="3">
+        <v>89296458991</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>15</v>
+      <c r="G10" s="17" t="s">
+        <v>24</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>16</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
-      <c r="M10" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="N10" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="O10" s="11" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="24" t="s">
-        <v>59</v>
+      <c r="M10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>157</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D11" s="25"/>
+        <v>158</v>
+      </c>
+      <c r="D11" s="25">
+        <v>7.65611981253432E+16</v>
+      </c>
       <c r="E11" s="3" t="s">
-        <v>61</v>
+        <v>159</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>25</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>16</v>
@@ -1264,36 +3190,1750 @@
       <c r="I11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="M11" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="N11" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="O11" s="11" t="s">
+      <c r="J11" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="N11" s="3">
+        <v>89166021553</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D12" s="25">
+        <v>7.6561198575429296E+16</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="N12" s="3">
+        <v>89856105867</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D13" s="25">
+        <v>7.6561198121186096E+16</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="N13" s="3">
+        <v>89164410288</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D14" s="25">
+        <v>7.6561198307056096E+16</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="N14" s="3">
+        <v>89156307637</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>13</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D15" s="25">
+        <v>7.65611980857692E+16</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J15" s="50" t="s">
+        <v>160</v>
+      </c>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="N15" s="3">
+        <v>89852215105</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>14</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" s="24">
+        <v>7.6561199012393296E+16</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J16" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="N16" s="3">
+        <v>89053306553</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>15</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17" s="24">
+        <v>7.6561199033920896E+16</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J17" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="N17" s="3">
+        <v>89047530977</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>16</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D18" s="24">
+        <v>7.6561198036146592E+16</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J18" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="N18" s="3">
+        <v>89376995199</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>17</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D19" s="24">
+        <v>7.6561198082738704E+16</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J19" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="N19" s="3">
+        <v>89880301405</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>18</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D20" s="24">
+        <v>7.6561198149906496E+16</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J20" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="N20" s="3">
+        <v>89177221138</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>19</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D21" s="24">
+        <v>1146157829</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J21" s="20">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>20</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" s="24">
+        <v>368217808</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J22" s="20">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>21</v>
+      </c>
+      <c r="B23" s="21"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J23" s="20">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>22</v>
+      </c>
+      <c r="B24" s="21"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J24" s="20">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>23</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" s="3"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J25" s="20">
+        <v>0</v>
+      </c>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>24</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="D26" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I26" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="K26" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="L26" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="M26" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="N26" s="13">
+        <v>89082432120</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>25</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>182</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I27" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="K27" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="L27" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="M27" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="N27" s="13" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>26</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I28" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="K28" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="L28" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="M28" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="N28" s="13" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>27</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>192</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I29" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="K29" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="L29" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="M29" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="N29" s="13" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>28</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="D30" s="25" t="s">
+        <v>198</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G30" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H30" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I30" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="K30" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="L30" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="M30" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="N30" s="13" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>29</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="D31" s="25" t="s">
+        <v>204</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I31" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="K31" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="L31" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="M31" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="N31" s="13" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>30</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D32" s="24">
+        <v>7.6561198186332E+16</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G32" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J32" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>31</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D33" s="24">
+        <v>7.6561198844516096E+16</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J33" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>32</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D34" s="24">
+        <v>7.65611981819036E+16</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G34" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J34" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>33</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D35" s="24">
+        <v>7.65611984191156E+16</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G35" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J35" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
         <v>34</v>
       </c>
+      <c r="B36" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D36" s="24">
+        <v>7.6561199016505104E+16</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G36" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J36" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="N36" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>35</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D37" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G37" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J37" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="K37" s="3"/>
+      <c r="L37" s="3"/>
+      <c r="M37" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="N37" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>36</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D38" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G38" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J38" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="N38" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <v>37</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D39" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G39" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J39" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="N39" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>38</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D40" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G40" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J40" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="K40" s="3"/>
+      <c r="L40" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="N40" s="3">
+        <v>89370252505</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>39</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D41" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G41" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J41" s="58" t="s">
+        <v>138</v>
+      </c>
+      <c r="K41" s="3"/>
+      <c r="L41" s="3"/>
+      <c r="M41" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>40</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="C42" s="3"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G42" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I42" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J42" s="28">
+        <v>3</v>
+      </c>
+      <c r="K42" s="3"/>
+      <c r="L42" s="3"/>
+      <c r="M42" s="3"/>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <v>41</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="C43" s="3"/>
+      <c r="D43" s="24"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G43" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I43" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J43" s="28">
+        <v>3</v>
+      </c>
+      <c r="K43" s="3"/>
+      <c r="L43" s="3"/>
+      <c r="M43" s="3"/>
+      <c r="N43" s="11" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>42</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="C44" s="3"/>
+      <c r="D44" s="24"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G44" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I44" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J44" s="28">
+        <v>3</v>
+      </c>
+      <c r="K44" s="3"/>
+      <c r="L44" s="3"/>
+      <c r="M44" s="3"/>
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <v>43</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="C45" s="3"/>
+      <c r="D45" s="24"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G45" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J45" s="28">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3"/>
+      <c r="L45" s="3"/>
+      <c r="M45" s="3"/>
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>44</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="C46" s="3"/>
+      <c r="D46" s="24"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G46" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I46" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J46" s="28">
+        <v>3</v>
+      </c>
+      <c r="K46" s="3"/>
+      <c r="L46" s="3"/>
+      <c r="M46" s="3"/>
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
+        <v>45</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D47" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J47" s="3"/>
+      <c r="K47" s="3"/>
+      <c r="L47" s="3"/>
+      <c r="M47" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O47" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <v>46</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D48" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G48" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J48" s="3"/>
+      <c r="K48" s="3"/>
+      <c r="L48" s="3"/>
+      <c r="M48" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="O48" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
+        <v>47</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D49" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J49" s="3"/>
+      <c r="K49" s="3"/>
+      <c r="L49" s="3"/>
+      <c r="M49" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>48</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D50" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G50" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J50" s="3"/>
+      <c r="K50" s="3"/>
+      <c r="L50" s="3"/>
+      <c r="M50" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="N50" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O50" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
+        <v>49</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D51" s="26" t="s">
+        <v>216</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="M51" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="N51" s="2">
+        <v>89017906169</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A52" s="30">
+        <v>19</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A53" s="30">
+        <v>23</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A54" s="30">
+        <v>41</v>
+      </c>
+      <c r="B54" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A55" s="30">
+        <v>7</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A56" s="30">
+        <v>7</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A57" s="30">
+        <v>8</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A58" s="30">
+        <v>8</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B59" s="70" t="s">
+        <v>239</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="D59" s="11">
+        <v>103993570</v>
+      </c>
+      <c r="E59" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="F59" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G59" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="H59" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I59" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J59" s="11"/>
+      <c r="K59" s="11"/>
+      <c r="L59" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="M59" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="N59" s="71" t="s">
+        <v>238</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="J5:J8"/>
-  </mergeCells>
+  <autoFilter ref="B2:O50" xr:uid="{EF88F6F3-0D6A-4594-A26D-5FF47BF11826}">
+    <sortState ref="B3:O50">
+      <sortCondition ref="G2:G50"/>
+    </sortState>
+  </autoFilter>
   <hyperlinks>
-    <hyperlink ref="M10" r:id="rId1" xr:uid="{651D084D-EAEF-4D6D-B5FA-5AACC9C8A44C}"/>
-    <hyperlink ref="M6" r:id="rId2" xr:uid="{B9E81AD7-FAA5-42A5-B634-51FDBF096A81}"/>
-    <hyperlink ref="M11" r:id="rId3" xr:uid="{33F0945F-2426-4C9D-A4C5-103DA7A4C69B}"/>
+    <hyperlink ref="M48" r:id="rId1" xr:uid="{651D084D-EAEF-4D6D-B5FA-5AACC9C8A44C}"/>
+    <hyperlink ref="M22" r:id="rId2" xr:uid="{B9E81AD7-FAA5-42A5-B634-51FDBF096A81}"/>
+    <hyperlink ref="M8" r:id="rId3" xr:uid="{33F0945F-2426-4C9D-A4C5-103DA7A4C69B}"/>
+    <hyperlink ref="M10" r:id="rId4" display="mailto:evgeny.chependyuk@lukoil.com" xr:uid="{C4812DF4-CB6C-4C65-AE46-5AA6F4CD1EBB}"/>
+    <hyperlink ref="M26" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="M27" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="M30" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="M29" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="M28" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="M31" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="M59" r:id="rId11" xr:uid="{9339DB2F-10E5-4884-B9B4-3521E74ECA67}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
-  <legacyDrawing r:id="rId5"/>
+  <pageSetup paperSize="9" scale="30" orientation="portrait" r:id="rId12"/>
+  <legacyDrawing r:id="rId13"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="10">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F81C753F-0D89-4F4B-A8D6-AD0486A119D8}">
           <x14:formula1>
             <xm:f>Справочник!$B$3:$B$5</xm:f>
@@ -1316,43 +4956,19 @@
           <x14:formula1>
             <xm:f>'C:\Users\izrantsevavs\AppData\Local\Microsoft\Windows\INetCache\Content.Outlook\FU2L8KB1\[Заявка на участие Шестаков.xlsx]Справочник'!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>I10</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{61964D9C-38C6-4E4E-94CA-8D769DBD7E0D}">
-          <x14:formula1>
-            <xm:f>'C:\Users\izrantsevavs\AppData\Local\Microsoft\Windows\INetCache\Content.Outlook\FU2L8KB1\[Заявка на участие Шестаков.xlsx]Справочник'!#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>H10</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4B63F609-1052-45C8-AF16-3DC411F4F1ED}">
-          <x14:formula1>
-            <xm:f>'C:\Users\izrantsevavs\AppData\Local\Microsoft\Windows\INetCache\Content.Outlook\FU2L8KB1\[Заявка на участие Шестаков.xlsx]Справочник'!#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>G10</xm:sqref>
+          <xm:sqref>G10:I10</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D394B3A8-3F60-489A-8389-9F45A1412F05}">
           <x14:formula1>
             <xm:f>'C:\Users\izrantsevavs\AppData\Local\Microsoft\Windows\INetCache\Content.Outlook\FU2L8KB1\[Заявка на участие_ПВВ.xlsx]Справочник'!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>I11</xm:sqref>
+          <xm:sqref>F11 H11:I11</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C8D66D48-D27D-4FE0-8A54-16285771590C}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E7FEAF4E-AA0F-4BFE-9B10-BC60658F97A1}">
           <x14:formula1>
-            <xm:f>'C:\Users\izrantsevavs\AppData\Local\Microsoft\Windows\INetCache\Content.Outlook\FU2L8KB1\[Заявка на участие_ПВВ.xlsx]Справочник'!#REF!</xm:f>
+            <xm:f>'C:\Users\izrantsevavs\AppData\Local\Microsoft\Windows\INetCache\Content.Outlook\FU2L8KB1\[Копия Заявка на участие.xlsx]Справочник'!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>H11</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E0C6D3E0-E919-43FD-83DE-139A0D3967D1}">
-          <x14:formula1>
-            <xm:f>'C:\Users\izrantsevavs\AppData\Local\Microsoft\Windows\INetCache\Content.Outlook\FU2L8KB1\[Заявка на участие_ПВВ.xlsx]Справочник'!#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>G11</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1D94299C-6DB2-471C-AE0A-85E6352BA979}">
-          <x14:formula1>
-            <xm:f>'C:\Users\izrantsevavs\AppData\Local\Microsoft\Windows\INetCache\Content.Outlook\FU2L8KB1\[Заявка на участие_ПВВ.xlsx]Справочник'!#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>F11</xm:sqref>
+          <xm:sqref>F59:I59</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1361,6 +4977,3294 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DFD92C5-86CA-4E7C-82FA-0A81F3E1069A}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:D51"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B2" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" s="69"/>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B3" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="69"/>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B4" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D4" s="69"/>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B5" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D5" s="69"/>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B6" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D6" s="69"/>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="69"/>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D8" s="69"/>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" s="69"/>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B10" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D10" s="69"/>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B11" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D11" s="69"/>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B12" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D12" s="69"/>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D13" s="69"/>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B14" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D14" s="69"/>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B15" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="69"/>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B16" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" s="69"/>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B17" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="69"/>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B18" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D18" s="69"/>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B19" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19" s="69"/>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B20" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="69"/>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B21" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="69"/>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B22" s="68" t="s">
+        <v>233</v>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="69"/>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B23" s="68" t="s">
+        <v>234</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="D23" s="69"/>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="69"/>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B25" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="D25" s="69"/>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B26" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="D26" s="69"/>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B27" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="D27" s="69"/>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B28" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="D28" s="69"/>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B29" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="D29" s="69"/>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B30" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="D30" s="69"/>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B31" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D31" s="69"/>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B32" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D32" s="69"/>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B33" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D33" s="69"/>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B34" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D34" s="69"/>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B35" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D35" s="69"/>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B36" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D36" s="69"/>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B37" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D37" s="69"/>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B38" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D38" s="69"/>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B39" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D39" s="69"/>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B40" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D40" s="69"/>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B41" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="C41" s="3"/>
+      <c r="D41" s="69"/>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B42" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="C42" s="3"/>
+      <c r="D42" s="69"/>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B43" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="C43" s="3"/>
+      <c r="D43" s="69"/>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B44" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="C44" s="3"/>
+      <c r="D44" s="69"/>
+    </row>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B45" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="C45" s="3"/>
+      <c r="D45" s="69"/>
+    </row>
+    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B46" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D46" s="69"/>
+    </row>
+    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B47" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D47" s="69"/>
+    </row>
+    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B48" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D48" s="69"/>
+    </row>
+    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B49" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D49" s="69"/>
+    </row>
+    <row r="50" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B50" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D50" s="69"/>
+    </row>
+    <row r="51" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B51" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="C51" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="D51" s="69"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C47" r:id="rId1" xr:uid="{0A27346D-DF1F-425C-BC1C-AA32AF05C285}"/>
+    <hyperlink ref="C21" r:id="rId2" xr:uid="{7EA275BF-F5FF-4445-80C0-D0DC0D195914}"/>
+    <hyperlink ref="C7" r:id="rId3" xr:uid="{942BBC76-9807-4A1C-892F-1E2F7D450997}"/>
+    <hyperlink ref="C9" r:id="rId4" display="mailto:evgeny.chependyuk@lukoil.com" xr:uid="{490E1461-AB4D-4F22-8663-21A3BECB9E39}"/>
+    <hyperlink ref="C25" r:id="rId5" xr:uid="{99E98A26-A983-48AE-A900-A879D698A6D7}"/>
+    <hyperlink ref="C26" r:id="rId6" xr:uid="{B4D8DCAE-FDD6-44BE-BFE2-EB0BEDE0F771}"/>
+    <hyperlink ref="C29" r:id="rId7" xr:uid="{832CD357-BAA7-483B-A2EC-B29F65CCD039}"/>
+    <hyperlink ref="C28" r:id="rId8" xr:uid="{3EEB6A5B-1103-4F07-AE4F-05529866E884}"/>
+    <hyperlink ref="C27" r:id="rId9" xr:uid="{6CEDA55F-582E-454B-91D4-257CC2DD7D97}"/>
+    <hyperlink ref="C30" r:id="rId10" xr:uid="{C8C2A3A3-43D0-49F0-A785-BBFC3CE665C2}"/>
+    <hyperlink ref="C23" r:id="rId11" xr:uid="{7B0CDE6C-0A45-4EE4-B1EC-D5A354AD2DC1}"/>
+    <hyperlink ref="C51" r:id="rId12" xr:uid="{6C030DEC-886A-4D7D-BFF0-2200FF795D91}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="88" orientation="portrait" r:id="rId13"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53926310-AF75-42C1-9349-F1FA49FF8102}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:I62"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="18" style="31" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" style="31" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="31" customWidth="1"/>
+    <col min="5" max="5" width="8.28515625" style="31" customWidth="1"/>
+    <col min="6" max="6" width="32.85546875" style="37" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.85546875" style="31" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:9" s="32" customFormat="1" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>366</v>
+      </c>
+      <c r="E2" s="34" t="s">
+        <v>221</v>
+      </c>
+      <c r="F2" s="34" t="s">
+        <v>222</v>
+      </c>
+      <c r="G2" s="35" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B3" s="114" t="s">
+        <v>225</v>
+      </c>
+      <c r="C3" s="111" t="s">
+        <v>224</v>
+      </c>
+      <c r="D3" s="111" t="s">
+        <v>224</v>
+      </c>
+      <c r="E3" s="41">
+        <v>1</v>
+      </c>
+      <c r="F3" s="46" t="s">
+        <v>90</v>
+      </c>
+      <c r="G3" s="42" t="s">
+        <v>226</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B4" s="115"/>
+      <c r="C4" s="112"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="39">
+        <v>2</v>
+      </c>
+      <c r="F4" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="G4" s="43" t="s">
+        <v>226</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B5" s="115"/>
+      <c r="C5" s="112"/>
+      <c r="D5" s="112"/>
+      <c r="E5" s="39">
+        <v>3</v>
+      </c>
+      <c r="F5" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="G5" s="43" t="s">
+        <v>226</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B6" s="115"/>
+      <c r="C6" s="112"/>
+      <c r="D6" s="112"/>
+      <c r="E6" s="39">
+        <v>4</v>
+      </c>
+      <c r="F6" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="G6" s="43" t="s">
+        <v>226</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="115"/>
+      <c r="C7" s="113"/>
+      <c r="D7" s="113"/>
+      <c r="E7" s="44">
+        <v>5</v>
+      </c>
+      <c r="F7" s="47" t="s">
+        <v>102</v>
+      </c>
+      <c r="G7" s="48" t="s">
+        <v>226</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B8" s="115"/>
+      <c r="C8" s="111" t="s">
+        <v>227</v>
+      </c>
+      <c r="D8" s="111" t="s">
+        <v>227</v>
+      </c>
+      <c r="E8" s="41">
+        <v>1</v>
+      </c>
+      <c r="F8" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8" s="42" t="s">
+        <v>226</v>
+      </c>
+      <c r="H8">
+        <v>6</v>
+      </c>
+      <c r="I8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B9" s="115"/>
+      <c r="C9" s="112"/>
+      <c r="D9" s="112"/>
+      <c r="E9" s="39">
+        <v>2</v>
+      </c>
+      <c r="F9" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9" s="43" t="s">
+        <v>226</v>
+      </c>
+      <c r="H9">
+        <v>7</v>
+      </c>
+      <c r="I9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B10" s="115"/>
+      <c r="C10" s="112"/>
+      <c r="D10" s="112"/>
+      <c r="E10" s="39">
+        <v>3</v>
+      </c>
+      <c r="F10" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="G10" s="43" t="s">
+        <v>226</v>
+      </c>
+      <c r="H10">
+        <v>8</v>
+      </c>
+      <c r="I10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B11" s="115"/>
+      <c r="C11" s="112"/>
+      <c r="D11" s="112"/>
+      <c r="E11" s="39">
+        <v>4</v>
+      </c>
+      <c r="F11" s="59" t="s">
+        <v>214</v>
+      </c>
+      <c r="G11" s="43" t="s">
+        <v>226</v>
+      </c>
+      <c r="H11">
+        <v>9</v>
+      </c>
+      <c r="I11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="116"/>
+      <c r="C12" s="113"/>
+      <c r="D12" s="113"/>
+      <c r="E12" s="44">
+        <v>5</v>
+      </c>
+      <c r="F12" s="124" t="s">
+        <v>361</v>
+      </c>
+      <c r="G12" s="45" t="s">
+        <v>226</v>
+      </c>
+      <c r="H12">
+        <v>10</v>
+      </c>
+      <c r="I12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="120" t="s">
+        <v>228</v>
+      </c>
+      <c r="C13" s="111" t="s">
+        <v>224</v>
+      </c>
+      <c r="D13" s="117" t="s">
+        <v>160</v>
+      </c>
+      <c r="E13" s="41">
+        <v>1</v>
+      </c>
+      <c r="F13" s="38" t="s">
+        <v>157</v>
+      </c>
+      <c r="G13" s="42" t="s">
+        <v>226</v>
+      </c>
+      <c r="H13">
+        <v>11</v>
+      </c>
+      <c r="I13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B14" s="121"/>
+      <c r="C14" s="112"/>
+      <c r="D14" s="112"/>
+      <c r="E14" s="39">
+        <v>2</v>
+      </c>
+      <c r="F14" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="G14" s="43" t="s">
+        <v>226</v>
+      </c>
+      <c r="H14">
+        <v>12</v>
+      </c>
+      <c r="I14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B15" s="121"/>
+      <c r="C15" s="112"/>
+      <c r="D15" s="112"/>
+      <c r="E15" s="39">
+        <v>3</v>
+      </c>
+      <c r="F15" s="38" t="s">
+        <v>165</v>
+      </c>
+      <c r="G15" s="43" t="s">
+        <v>226</v>
+      </c>
+      <c r="H15">
+        <v>13</v>
+      </c>
+      <c r="I15">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B16" s="121"/>
+      <c r="C16" s="112"/>
+      <c r="D16" s="112"/>
+      <c r="E16" s="39">
+        <v>4</v>
+      </c>
+      <c r="F16" s="38" t="s">
+        <v>168</v>
+      </c>
+      <c r="G16" s="43" t="s">
+        <v>226</v>
+      </c>
+      <c r="H16">
+        <v>14</v>
+      </c>
+      <c r="I16">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="121"/>
+      <c r="C17" s="113"/>
+      <c r="D17" s="113"/>
+      <c r="E17" s="44">
+        <v>5</v>
+      </c>
+      <c r="F17" s="38" t="s">
+        <v>171</v>
+      </c>
+      <c r="G17" s="48" t="s">
+        <v>226</v>
+      </c>
+      <c r="H17">
+        <v>15</v>
+      </c>
+      <c r="I17">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="121"/>
+      <c r="C18" s="111" t="s">
+        <v>227</v>
+      </c>
+      <c r="D18" s="117" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" s="41">
+        <v>1</v>
+      </c>
+      <c r="F18" s="46" t="s">
+        <v>70</v>
+      </c>
+      <c r="G18" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="H18">
+        <v>16</v>
+      </c>
+      <c r="I18">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B19" s="121"/>
+      <c r="C19" s="112"/>
+      <c r="D19" s="112"/>
+      <c r="E19" s="39">
+        <v>2</v>
+      </c>
+      <c r="F19" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="G19" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="H19">
+        <v>17</v>
+      </c>
+      <c r="I19">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B20" s="121"/>
+      <c r="C20" s="112"/>
+      <c r="D20" s="112"/>
+      <c r="E20" s="39">
+        <v>3</v>
+      </c>
+      <c r="F20" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="G20" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="H20">
+        <v>18</v>
+      </c>
+      <c r="I20">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B21" s="121"/>
+      <c r="C21" s="112"/>
+      <c r="D21" s="112"/>
+      <c r="E21" s="39">
+        <v>4</v>
+      </c>
+      <c r="F21" s="59" t="s">
+        <v>83</v>
+      </c>
+      <c r="G21" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="H21">
+        <v>19</v>
+      </c>
+      <c r="I21">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="121"/>
+      <c r="C22" s="113"/>
+      <c r="D22" s="112"/>
+      <c r="E22" s="44">
+        <v>5</v>
+      </c>
+      <c r="F22" s="49" t="s">
+        <v>86</v>
+      </c>
+      <c r="G22" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="H22">
+        <v>20</v>
+      </c>
+      <c r="I22">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B23" s="121"/>
+      <c r="C23" s="117" t="s">
+        <v>378</v>
+      </c>
+      <c r="D23" s="142" t="s">
+        <v>177</v>
+      </c>
+      <c r="E23" s="132">
+        <v>1</v>
+      </c>
+      <c r="F23" s="61" t="s">
+        <v>174</v>
+      </c>
+      <c r="G23" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="H23">
+        <v>21</v>
+      </c>
+      <c r="I23">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B24" s="121"/>
+      <c r="C24" s="118"/>
+      <c r="D24" s="143"/>
+      <c r="E24" s="133">
+        <v>2</v>
+      </c>
+      <c r="F24" s="62" t="s">
+        <v>180</v>
+      </c>
+      <c r="G24" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="H24">
+        <v>22</v>
+      </c>
+      <c r="I24">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B25" s="121"/>
+      <c r="C25" s="118"/>
+      <c r="D25" s="143"/>
+      <c r="E25" s="133">
+        <v>3</v>
+      </c>
+      <c r="F25" s="62" t="s">
+        <v>185</v>
+      </c>
+      <c r="G25" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="H25">
+        <v>23</v>
+      </c>
+      <c r="I25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B26" s="121"/>
+      <c r="C26" s="118"/>
+      <c r="D26" s="143"/>
+      <c r="E26" s="133">
+        <v>4</v>
+      </c>
+      <c r="F26" s="62" t="s">
+        <v>190</v>
+      </c>
+      <c r="G26" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="H26">
+        <v>24</v>
+      </c>
+      <c r="I26">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B27" s="121"/>
+      <c r="C27" s="118"/>
+      <c r="D27" s="143"/>
+      <c r="E27" s="133">
+        <v>5</v>
+      </c>
+      <c r="F27" s="62" t="s">
+        <v>196</v>
+      </c>
+      <c r="G27" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="H27">
+        <v>25</v>
+      </c>
+      <c r="I27">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="121"/>
+      <c r="C28" s="119"/>
+      <c r="D28" s="144"/>
+      <c r="E28" s="141">
+        <v>6</v>
+      </c>
+      <c r="F28" s="63" t="s">
+        <v>202</v>
+      </c>
+      <c r="G28" s="45" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B29" s="121"/>
+      <c r="C29" s="131" t="s">
+        <v>380</v>
+      </c>
+      <c r="D29" s="135" t="s">
+        <v>381</v>
+      </c>
+      <c r="E29" s="132">
+        <v>1</v>
+      </c>
+      <c r="F29" s="62" t="s">
+        <v>243</v>
+      </c>
+      <c r="G29" s="42" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B30" s="121"/>
+      <c r="C30" s="115"/>
+      <c r="D30" s="136"/>
+      <c r="E30" s="133">
+        <v>2</v>
+      </c>
+      <c r="F30" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="G30" s="43" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B31" s="121"/>
+      <c r="C31" s="115"/>
+      <c r="D31" s="136"/>
+      <c r="E31" s="133">
+        <v>3</v>
+      </c>
+      <c r="F31" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="G31" s="43" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B32" s="121"/>
+      <c r="C32" s="115"/>
+      <c r="D32" s="136"/>
+      <c r="E32" s="133">
+        <v>4</v>
+      </c>
+      <c r="F32" s="60"/>
+      <c r="G32" s="43" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="121"/>
+      <c r="C33" s="115"/>
+      <c r="D33" s="137"/>
+      <c r="E33" s="134">
+        <v>5</v>
+      </c>
+      <c r="F33" s="56"/>
+      <c r="G33" s="57"/>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B34" s="121"/>
+      <c r="C34" s="117" t="s">
+        <v>379</v>
+      </c>
+      <c r="D34" s="117" t="s">
+        <v>112</v>
+      </c>
+      <c r="E34" s="41">
+        <v>1</v>
+      </c>
+      <c r="F34" s="61" t="s">
+        <v>109</v>
+      </c>
+      <c r="G34" s="42" t="s">
+        <v>226</v>
+      </c>
+      <c r="H34">
+        <v>32</v>
+      </c>
+      <c r="I34">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B35" s="121"/>
+      <c r="C35" s="118"/>
+      <c r="D35" s="118"/>
+      <c r="E35" s="39">
+        <v>2</v>
+      </c>
+      <c r="F35" s="62" t="s">
+        <v>116</v>
+      </c>
+      <c r="G35" s="53" t="s">
+        <v>226</v>
+      </c>
+      <c r="H35">
+        <v>33</v>
+      </c>
+      <c r="I35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B36" s="121"/>
+      <c r="C36" s="118"/>
+      <c r="D36" s="118"/>
+      <c r="E36" s="39">
+        <v>3</v>
+      </c>
+      <c r="F36" s="62" t="s">
+        <v>121</v>
+      </c>
+      <c r="G36" s="53" t="s">
+        <v>226</v>
+      </c>
+      <c r="H36">
+        <v>34</v>
+      </c>
+      <c r="I36">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B37" s="121"/>
+      <c r="C37" s="118"/>
+      <c r="D37" s="118"/>
+      <c r="E37" s="39">
+        <v>4</v>
+      </c>
+      <c r="F37" s="62" t="s">
+        <v>125</v>
+      </c>
+      <c r="G37" s="53" t="s">
+        <v>226</v>
+      </c>
+      <c r="H37">
+        <v>35</v>
+      </c>
+      <c r="I37">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="122"/>
+      <c r="C38" s="119"/>
+      <c r="D38" s="119"/>
+      <c r="E38" s="44">
+        <v>5</v>
+      </c>
+      <c r="F38" s="63" t="s">
+        <v>130</v>
+      </c>
+      <c r="G38" s="45" t="s">
+        <v>226</v>
+      </c>
+      <c r="H38">
+        <v>36</v>
+      </c>
+      <c r="I38">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B39" s="114" t="s">
+        <v>229</v>
+      </c>
+      <c r="C39" s="117" t="s">
+        <v>224</v>
+      </c>
+      <c r="D39" s="117" t="s">
+        <v>138</v>
+      </c>
+      <c r="E39" s="41">
+        <v>1</v>
+      </c>
+      <c r="F39" s="46" t="s">
+        <v>135</v>
+      </c>
+      <c r="G39" s="42" t="s">
+        <v>226</v>
+      </c>
+      <c r="H39">
+        <v>37</v>
+      </c>
+      <c r="I39">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B40" s="115"/>
+      <c r="C40" s="112"/>
+      <c r="D40" s="112"/>
+      <c r="E40" s="39">
+        <v>2</v>
+      </c>
+      <c r="F40" s="38" t="s">
+        <v>141</v>
+      </c>
+      <c r="G40" s="43" t="s">
+        <v>226</v>
+      </c>
+      <c r="H40">
+        <v>38</v>
+      </c>
+      <c r="I40">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B41" s="115"/>
+      <c r="C41" s="112"/>
+      <c r="D41" s="112"/>
+      <c r="E41" s="39">
+        <v>3</v>
+      </c>
+      <c r="F41" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="G41" s="43" t="s">
+        <v>226</v>
+      </c>
+      <c r="H41">
+        <v>39</v>
+      </c>
+      <c r="I41">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B42" s="115"/>
+      <c r="C42" s="112"/>
+      <c r="D42" s="112"/>
+      <c r="E42" s="39">
+        <v>4</v>
+      </c>
+      <c r="F42" s="38" t="s">
+        <v>153</v>
+      </c>
+      <c r="G42" s="43" t="s">
+        <v>226</v>
+      </c>
+      <c r="H42">
+        <v>40</v>
+      </c>
+      <c r="I42">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B43" s="115"/>
+      <c r="C43" s="113"/>
+      <c r="D43" s="113"/>
+      <c r="E43" s="44">
+        <v>5</v>
+      </c>
+      <c r="F43" s="47" t="s">
+        <v>149</v>
+      </c>
+      <c r="G43" s="48" t="s">
+        <v>17</v>
+      </c>
+      <c r="H43">
+        <v>41</v>
+      </c>
+      <c r="I43">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B44" s="115"/>
+      <c r="C44" s="117" t="s">
+        <v>227</v>
+      </c>
+      <c r="D44" s="117"/>
+      <c r="E44" s="41">
+        <v>1</v>
+      </c>
+      <c r="F44" s="61" t="s">
+        <v>230</v>
+      </c>
+      <c r="G44" s="42" t="s">
+        <v>226</v>
+      </c>
+      <c r="H44">
+        <v>42</v>
+      </c>
+      <c r="I44">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B45" s="115"/>
+      <c r="C45" s="112"/>
+      <c r="D45" s="112"/>
+      <c r="E45" s="39">
+        <v>2</v>
+      </c>
+      <c r="F45" s="62" t="s">
+        <v>231</v>
+      </c>
+      <c r="G45" s="43" t="s">
+        <v>226</v>
+      </c>
+      <c r="H45">
+        <v>43</v>
+      </c>
+      <c r="I45">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B46" s="115"/>
+      <c r="C46" s="112"/>
+      <c r="D46" s="112"/>
+      <c r="E46" s="39">
+        <v>3</v>
+      </c>
+      <c r="F46" s="62" t="s">
+        <v>232</v>
+      </c>
+      <c r="G46" s="43" t="s">
+        <v>226</v>
+      </c>
+      <c r="H46">
+        <v>44</v>
+      </c>
+      <c r="I46">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B47" s="115"/>
+      <c r="C47" s="112"/>
+      <c r="D47" s="112"/>
+      <c r="E47" s="39">
+        <v>4</v>
+      </c>
+      <c r="F47" s="64" t="s">
+        <v>211</v>
+      </c>
+      <c r="G47" s="43" t="s">
+        <v>226</v>
+      </c>
+      <c r="H47">
+        <v>45</v>
+      </c>
+      <c r="I47">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="116"/>
+      <c r="C48" s="112"/>
+      <c r="D48" s="112"/>
+      <c r="E48" s="40">
+        <v>5</v>
+      </c>
+      <c r="F48" s="65" t="s">
+        <v>212</v>
+      </c>
+      <c r="G48" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="H48">
+        <v>46</v>
+      </c>
+      <c r="I48">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="114" t="s">
+        <v>14</v>
+      </c>
+      <c r="C49" s="138">
+        <v>1</v>
+      </c>
+      <c r="D49" s="127" t="s">
+        <v>367</v>
+      </c>
+      <c r="E49" s="41">
+        <v>1</v>
+      </c>
+      <c r="F49" s="46" t="s">
+        <v>35</v>
+      </c>
+      <c r="G49" s="42" t="s">
+        <v>226</v>
+      </c>
+      <c r="H49">
+        <v>47</v>
+      </c>
+      <c r="I49">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B50" s="115"/>
+      <c r="C50" s="139">
+        <v>2</v>
+      </c>
+      <c r="D50" s="128" t="s">
+        <v>368</v>
+      </c>
+      <c r="E50" s="39">
+        <v>2</v>
+      </c>
+      <c r="F50" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="G50" s="92" t="s">
+        <v>226</v>
+      </c>
+      <c r="H50">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B51" s="115"/>
+      <c r="C51" s="139">
+        <v>3</v>
+      </c>
+      <c r="D51" s="128" t="s">
+        <v>369</v>
+      </c>
+      <c r="E51" s="39">
+        <v>3</v>
+      </c>
+      <c r="F51" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="G51" s="92" t="s">
+        <v>226</v>
+      </c>
+      <c r="H51">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B52" s="115"/>
+      <c r="C52" s="139">
+        <v>4</v>
+      </c>
+      <c r="D52" s="128" t="s">
+        <v>370</v>
+      </c>
+      <c r="E52" s="39">
+        <v>4</v>
+      </c>
+      <c r="F52" s="62" t="s">
+        <v>231</v>
+      </c>
+      <c r="G52" s="92" t="s">
+        <v>226</v>
+      </c>
+      <c r="H52">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B53" s="115"/>
+      <c r="C53" s="139">
+        <v>5</v>
+      </c>
+      <c r="D53" s="128" t="s">
+        <v>371</v>
+      </c>
+      <c r="E53" s="39">
+        <v>5</v>
+      </c>
+      <c r="F53" s="62" t="s">
+        <v>244</v>
+      </c>
+      <c r="G53" s="92" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B54" s="115"/>
+      <c r="C54" s="139">
+        <v>6</v>
+      </c>
+      <c r="D54" s="128" t="s">
+        <v>377</v>
+      </c>
+      <c r="E54" s="39">
+        <v>6</v>
+      </c>
+      <c r="F54" s="62"/>
+      <c r="G54" s="92" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B55" s="115"/>
+      <c r="C55" s="139">
+        <v>7</v>
+      </c>
+      <c r="D55" s="128" t="s">
+        <v>372</v>
+      </c>
+      <c r="E55" s="39">
+        <v>7</v>
+      </c>
+      <c r="F55" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="G55" s="92" t="s">
+        <v>226</v>
+      </c>
+      <c r="H55">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B56" s="116"/>
+      <c r="C56" s="140">
+        <v>8</v>
+      </c>
+      <c r="D56" s="129" t="s">
+        <v>373</v>
+      </c>
+      <c r="E56" s="44">
+        <v>8</v>
+      </c>
+      <c r="F56" s="63" t="s">
+        <v>66</v>
+      </c>
+      <c r="G56" s="93" t="s">
+        <v>226</v>
+      </c>
+      <c r="H56">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="57" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B57" s="114" t="s">
+        <v>15</v>
+      </c>
+      <c r="C57" s="130">
+        <v>1</v>
+      </c>
+      <c r="D57" s="54" t="s">
+        <v>374</v>
+      </c>
+      <c r="E57" s="41">
+        <v>1</v>
+      </c>
+      <c r="F57" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="G57" s="42" t="s">
+        <v>226</v>
+      </c>
+      <c r="H57">
+        <v>53</v>
+      </c>
+      <c r="I57">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="58" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B58" s="115"/>
+      <c r="C58" s="55">
+        <v>2</v>
+      </c>
+      <c r="D58" s="55" t="s">
+        <v>375</v>
+      </c>
+      <c r="E58" s="39">
+        <v>2</v>
+      </c>
+      <c r="F58" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="G58" s="53" t="s">
+        <v>226</v>
+      </c>
+      <c r="H58">
+        <v>54</v>
+      </c>
+      <c r="I58">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="59" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B59" s="115"/>
+      <c r="C59" s="55">
+        <v>3</v>
+      </c>
+      <c r="D59" s="55" t="s">
+        <v>376</v>
+      </c>
+      <c r="E59" s="39">
+        <v>3</v>
+      </c>
+      <c r="F59" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="G59" s="53" t="s">
+        <v>226</v>
+      </c>
+      <c r="H59">
+        <v>55</v>
+      </c>
+      <c r="I59">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="60" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B60" s="115"/>
+      <c r="C60" s="55">
+        <v>4</v>
+      </c>
+      <c r="D60" s="55" t="s">
+        <v>377</v>
+      </c>
+      <c r="E60" s="39">
+        <v>4</v>
+      </c>
+      <c r="F60" s="38"/>
+      <c r="G60" s="92" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B61" s="115"/>
+      <c r="C61" s="55">
+        <v>5</v>
+      </c>
+      <c r="D61" s="55" t="s">
+        <v>372</v>
+      </c>
+      <c r="E61" s="39">
+        <v>5</v>
+      </c>
+      <c r="F61" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="G61" s="92" t="s">
+        <v>226</v>
+      </c>
+      <c r="H61">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="62" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B62" s="116"/>
+      <c r="C62" s="66">
+        <v>6</v>
+      </c>
+      <c r="D62" s="67" t="s">
+        <v>373</v>
+      </c>
+      <c r="E62" s="44">
+        <v>6</v>
+      </c>
+      <c r="F62" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="G62" s="93" t="s">
+        <v>226</v>
+      </c>
+      <c r="H62">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataConsolidate/>
+  <mergeCells count="23">
+    <mergeCell ref="B49:B56"/>
+    <mergeCell ref="B57:B62"/>
+    <mergeCell ref="D29:D33"/>
+    <mergeCell ref="D23:D28"/>
+    <mergeCell ref="D34:D38"/>
+    <mergeCell ref="B13:B38"/>
+    <mergeCell ref="B39:B48"/>
+    <mergeCell ref="D39:D43"/>
+    <mergeCell ref="D44:D48"/>
+    <mergeCell ref="C13:C17"/>
+    <mergeCell ref="C18:C22"/>
+    <mergeCell ref="C29:C33"/>
+    <mergeCell ref="C23:C28"/>
+    <mergeCell ref="C34:C38"/>
+    <mergeCell ref="C39:C43"/>
+    <mergeCell ref="C44:C48"/>
+    <mergeCell ref="D3:D7"/>
+    <mergeCell ref="D8:D12"/>
+    <mergeCell ref="B3:B12"/>
+    <mergeCell ref="D13:D17"/>
+    <mergeCell ref="D18:D22"/>
+    <mergeCell ref="C3:C7"/>
+    <mergeCell ref="C8:C12"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="59" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE7205E2-1911-4B8E-9062-97E140B049B2}">
+  <dimension ref="A1:L26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="96"/>
+    <col min="2" max="2" width="17.28515625" style="97" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" style="97" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="97"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="98" t="s">
+        <v>302</v>
+      </c>
+      <c r="C2" s="99" t="s">
+        <v>303</v>
+      </c>
+      <c r="D2" s="98" t="s">
+        <v>247</v>
+      </c>
+      <c r="E2" s="98" t="s">
+        <v>249</v>
+      </c>
+      <c r="F2" s="98" t="s">
+        <v>343</v>
+      </c>
+      <c r="G2" s="98" t="s">
+        <v>255</v>
+      </c>
+      <c r="H2" s="98" t="s">
+        <v>263</v>
+      </c>
+      <c r="I2" s="98" t="s">
+        <v>269</v>
+      </c>
+      <c r="J2" s="98" t="s">
+        <v>346</v>
+      </c>
+      <c r="K2" s="98" t="s">
+        <v>347</v>
+      </c>
+      <c r="L2" s="98" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="100" t="s">
+        <v>304</v>
+      </c>
+      <c r="C3" s="101" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="102"/>
+      <c r="E3" s="103"/>
+      <c r="F3" s="103"/>
+      <c r="G3" s="103"/>
+      <c r="H3" s="103"/>
+      <c r="I3" s="103"/>
+      <c r="J3" s="103"/>
+      <c r="K3" s="103"/>
+      <c r="L3" s="103"/>
+    </row>
+    <row r="4" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="100" t="s">
+        <v>305</v>
+      </c>
+      <c r="C4" s="101" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="102"/>
+      <c r="E4" s="103"/>
+      <c r="F4" s="103"/>
+      <c r="G4" s="103"/>
+      <c r="H4" s="103"/>
+      <c r="I4" s="103"/>
+      <c r="J4" s="103"/>
+      <c r="K4" s="103"/>
+      <c r="L4" s="103"/>
+    </row>
+    <row r="5" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="100" t="s">
+        <v>306</v>
+      </c>
+      <c r="C5" s="101" t="s">
+        <v>307</v>
+      </c>
+      <c r="D5" s="103"/>
+      <c r="E5" s="103"/>
+      <c r="F5" s="103"/>
+      <c r="G5" s="103"/>
+      <c r="H5" s="104"/>
+      <c r="I5" s="103"/>
+      <c r="J5" s="103"/>
+      <c r="K5" s="103"/>
+      <c r="L5" s="103"/>
+    </row>
+    <row r="6" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="100" t="s">
+        <v>308</v>
+      </c>
+      <c r="C6" s="101" t="s">
+        <v>307</v>
+      </c>
+      <c r="D6" s="103"/>
+      <c r="E6" s="103"/>
+      <c r="F6" s="103"/>
+      <c r="G6" s="103"/>
+      <c r="H6" s="103"/>
+      <c r="I6" s="104"/>
+      <c r="J6" s="103"/>
+      <c r="K6" s="103"/>
+      <c r="L6" s="103"/>
+    </row>
+    <row r="7" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="123"/>
+      <c r="B7" s="100" t="s">
+        <v>309</v>
+      </c>
+      <c r="C7" s="101" t="s">
+        <v>307</v>
+      </c>
+      <c r="D7" s="103"/>
+      <c r="E7" s="103"/>
+      <c r="F7" s="103"/>
+      <c r="G7" s="103"/>
+      <c r="H7" s="103"/>
+      <c r="I7" s="103"/>
+      <c r="J7" s="104"/>
+      <c r="K7" s="103"/>
+      <c r="L7" s="103"/>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="123"/>
+      <c r="B8" s="100" t="s">
+        <v>363</v>
+      </c>
+      <c r="C8" s="101" t="s">
+        <v>307</v>
+      </c>
+      <c r="D8" s="103"/>
+      <c r="E8" s="103"/>
+      <c r="F8" s="103"/>
+      <c r="G8" s="103"/>
+      <c r="H8" s="126"/>
+      <c r="I8" s="103"/>
+      <c r="J8" s="103"/>
+      <c r="K8" s="103"/>
+      <c r="L8" s="103"/>
+    </row>
+    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="123"/>
+      <c r="B9" s="100" t="s">
+        <v>364</v>
+      </c>
+      <c r="C9" s="101" t="s">
+        <v>307</v>
+      </c>
+      <c r="D9" s="103"/>
+      <c r="E9" s="103"/>
+      <c r="F9" s="103"/>
+      <c r="G9" s="103"/>
+      <c r="H9" s="103"/>
+      <c r="I9" s="126"/>
+      <c r="J9" s="103"/>
+      <c r="K9" s="103"/>
+      <c r="L9" s="103"/>
+    </row>
+    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="123"/>
+      <c r="B10" s="100" t="s">
+        <v>365</v>
+      </c>
+      <c r="C10" s="101" t="s">
+        <v>307</v>
+      </c>
+      <c r="D10" s="103"/>
+      <c r="E10" s="103"/>
+      <c r="F10" s="103"/>
+      <c r="G10" s="103"/>
+      <c r="H10" s="103"/>
+      <c r="I10" s="103"/>
+      <c r="J10" s="126"/>
+      <c r="K10" s="103"/>
+      <c r="L10" s="103"/>
+    </row>
+    <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="123"/>
+      <c r="B11" s="100" t="s">
+        <v>310</v>
+      </c>
+      <c r="C11" s="101" t="s">
+        <v>307</v>
+      </c>
+      <c r="D11" s="103"/>
+      <c r="E11" s="105"/>
+      <c r="F11" s="103"/>
+      <c r="G11" s="103"/>
+      <c r="H11" s="103"/>
+      <c r="I11" s="103"/>
+      <c r="J11" s="103"/>
+      <c r="K11" s="103"/>
+      <c r="L11" s="103"/>
+    </row>
+    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="106"/>
+      <c r="B12" s="100" t="s">
+        <v>311</v>
+      </c>
+      <c r="C12" s="101" t="s">
+        <v>312</v>
+      </c>
+      <c r="D12" s="103"/>
+      <c r="E12" s="105"/>
+      <c r="F12" s="103"/>
+      <c r="G12" s="103"/>
+      <c r="H12" s="103"/>
+      <c r="I12" s="103"/>
+      <c r="J12" s="103"/>
+      <c r="K12" s="103"/>
+      <c r="L12" s="103"/>
+    </row>
+    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="106"/>
+      <c r="B13" s="100" t="s">
+        <v>313</v>
+      </c>
+      <c r="C13" s="101" t="s">
+        <v>314</v>
+      </c>
+      <c r="D13" s="103"/>
+      <c r="E13" s="103"/>
+      <c r="F13" s="105"/>
+      <c r="G13" s="103"/>
+      <c r="H13" s="103"/>
+      <c r="I13" s="103"/>
+      <c r="J13" s="103"/>
+      <c r="K13" s="103"/>
+      <c r="L13" s="103"/>
+    </row>
+    <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="106"/>
+      <c r="B14" s="100" t="s">
+        <v>315</v>
+      </c>
+      <c r="C14" s="101" t="s">
+        <v>316</v>
+      </c>
+      <c r="D14" s="103"/>
+      <c r="E14" s="103"/>
+      <c r="F14" s="105"/>
+      <c r="G14" s="103"/>
+      <c r="H14" s="103"/>
+      <c r="I14" s="103"/>
+      <c r="J14" s="103"/>
+      <c r="K14" s="103"/>
+      <c r="L14" s="103"/>
+    </row>
+    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="106"/>
+      <c r="B15" s="100" t="s">
+        <v>317</v>
+      </c>
+      <c r="C15" s="101" t="s">
+        <v>318</v>
+      </c>
+      <c r="D15" s="103"/>
+      <c r="E15" s="103"/>
+      <c r="F15" s="103"/>
+      <c r="G15" s="103"/>
+      <c r="H15" s="105"/>
+      <c r="I15" s="103"/>
+      <c r="J15" s="103"/>
+      <c r="K15" s="103"/>
+      <c r="L15" s="103"/>
+    </row>
+    <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="106"/>
+      <c r="B16" s="100" t="s">
+        <v>319</v>
+      </c>
+      <c r="C16" s="101" t="s">
+        <v>320</v>
+      </c>
+      <c r="D16" s="103"/>
+      <c r="E16" s="103"/>
+      <c r="F16" s="103"/>
+      <c r="G16" s="103"/>
+      <c r="H16" s="105"/>
+      <c r="I16" s="103"/>
+      <c r="J16" s="103"/>
+      <c r="K16" s="103"/>
+      <c r="L16" s="103"/>
+    </row>
+    <row r="17" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="106"/>
+      <c r="B17" s="100" t="s">
+        <v>321</v>
+      </c>
+      <c r="C17" s="101" t="s">
+        <v>322</v>
+      </c>
+      <c r="D17" s="103"/>
+      <c r="E17" s="103"/>
+      <c r="F17" s="103"/>
+      <c r="G17" s="103"/>
+      <c r="H17" s="103"/>
+      <c r="I17" s="105"/>
+      <c r="J17" s="103"/>
+      <c r="K17" s="103"/>
+      <c r="L17" s="103"/>
+    </row>
+    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="106"/>
+      <c r="B18" s="100" t="s">
+        <v>323</v>
+      </c>
+      <c r="C18" s="101" t="s">
+        <v>324</v>
+      </c>
+      <c r="D18" s="103"/>
+      <c r="E18" s="103"/>
+      <c r="F18" s="103"/>
+      <c r="G18" s="103"/>
+      <c r="H18" s="103"/>
+      <c r="I18" s="105"/>
+      <c r="J18" s="103"/>
+      <c r="K18" s="103"/>
+      <c r="L18" s="103"/>
+    </row>
+    <row r="19" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="106"/>
+      <c r="B19" s="100" t="s">
+        <v>325</v>
+      </c>
+      <c r="C19" s="101" t="s">
+        <v>326</v>
+      </c>
+      <c r="D19" s="103"/>
+      <c r="E19" s="103"/>
+      <c r="F19" s="103"/>
+      <c r="G19" s="103"/>
+      <c r="H19" s="103"/>
+      <c r="I19" s="103"/>
+      <c r="J19" s="105"/>
+      <c r="K19" s="103"/>
+      <c r="L19" s="103"/>
+    </row>
+    <row r="20" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="106"/>
+      <c r="B20" s="100" t="s">
+        <v>327</v>
+      </c>
+      <c r="C20" s="101" t="s">
+        <v>328</v>
+      </c>
+      <c r="D20" s="103"/>
+      <c r="E20" s="103"/>
+      <c r="F20" s="103"/>
+      <c r="G20" s="103"/>
+      <c r="H20" s="103"/>
+      <c r="I20" s="103"/>
+      <c r="J20" s="105"/>
+      <c r="K20" s="103"/>
+      <c r="L20" s="103"/>
+    </row>
+    <row r="21" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="100" t="s">
+        <v>329</v>
+      </c>
+      <c r="C21" s="101" t="s">
+        <v>330</v>
+      </c>
+      <c r="D21" s="103"/>
+      <c r="E21" s="107"/>
+      <c r="F21" s="103"/>
+      <c r="G21" s="103"/>
+      <c r="H21" s="108"/>
+      <c r="I21" s="108"/>
+      <c r="J21" s="108"/>
+      <c r="K21" s="103"/>
+      <c r="L21" s="103"/>
+    </row>
+    <row r="22" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="100" t="s">
+        <v>331</v>
+      </c>
+      <c r="C22" s="101" t="s">
+        <v>332</v>
+      </c>
+      <c r="D22" s="103"/>
+      <c r="E22" s="103"/>
+      <c r="F22" s="107"/>
+      <c r="G22" s="103"/>
+      <c r="H22" s="108"/>
+      <c r="I22" s="108"/>
+      <c r="J22" s="108"/>
+      <c r="K22" s="103"/>
+      <c r="L22" s="103"/>
+    </row>
+    <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="100" t="s">
+        <v>333</v>
+      </c>
+      <c r="C23" s="101" t="s">
+        <v>334</v>
+      </c>
+      <c r="D23" s="103"/>
+      <c r="E23" s="103"/>
+      <c r="F23" s="103"/>
+      <c r="G23" s="103"/>
+      <c r="H23" s="103"/>
+      <c r="I23" s="103"/>
+      <c r="J23" s="103"/>
+      <c r="K23" s="109"/>
+      <c r="L23" s="103"/>
+    </row>
+    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="100" t="s">
+        <v>336</v>
+      </c>
+      <c r="C24" s="101" t="s">
+        <v>335</v>
+      </c>
+      <c r="D24" s="103"/>
+      <c r="E24" s="103"/>
+      <c r="F24" s="103"/>
+      <c r="G24" s="110"/>
+      <c r="H24" s="103"/>
+      <c r="I24" s="103"/>
+      <c r="J24" s="103"/>
+      <c r="K24" s="103"/>
+      <c r="L24" s="103"/>
+    </row>
+    <row r="25" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="100" t="s">
+        <v>276</v>
+      </c>
+      <c r="C25" s="101" t="s">
+        <v>335</v>
+      </c>
+      <c r="D25" s="103"/>
+      <c r="E25" s="103"/>
+      <c r="F25" s="103"/>
+      <c r="G25" s="103"/>
+      <c r="H25" s="103"/>
+      <c r="I25" s="103"/>
+      <c r="J25" s="103"/>
+      <c r="K25" s="103"/>
+      <c r="L25" s="102"/>
+    </row>
+    <row r="26" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="100" t="s">
+        <v>337</v>
+      </c>
+      <c r="C26" s="101" t="s">
+        <v>335</v>
+      </c>
+      <c r="D26" s="103"/>
+      <c r="E26" s="103"/>
+      <c r="F26" s="103"/>
+      <c r="G26" s="103"/>
+      <c r="H26" s="103"/>
+      <c r="I26" s="103"/>
+      <c r="J26" s="103"/>
+      <c r="K26" s="103"/>
+      <c r="L26" s="102"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A7:A11"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11234D94-E616-4689-B6E6-FA6FF69EDA77}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="C1:I29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="0" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="45.140625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" customWidth="1"/>
+    <col min="8" max="8" width="12.42578125" customWidth="1"/>
+    <col min="9" max="9" width="45.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>338</v>
+      </c>
+      <c r="I1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="2" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="72" t="s">
+        <v>245</v>
+      </c>
+      <c r="D3" s="73" t="s">
+        <v>246</v>
+      </c>
+      <c r="E3" s="73" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="4" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="74" t="s">
+        <v>247</v>
+      </c>
+      <c r="D4" s="75" t="s">
+        <v>248</v>
+      </c>
+      <c r="E4" s="75" t="s">
+        <v>278</v>
+      </c>
+      <c r="G4" s="72" t="s">
+        <v>384</v>
+      </c>
+      <c r="H4" s="73" t="s">
+        <v>383</v>
+      </c>
+      <c r="I4" s="73" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="5" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C5" s="94" t="s">
+        <v>249</v>
+      </c>
+      <c r="D5" s="95" t="s">
+        <v>281</v>
+      </c>
+      <c r="E5" s="95" t="s">
+        <v>264</v>
+      </c>
+      <c r="G5" s="94" t="s">
+        <v>382</v>
+      </c>
+      <c r="H5" s="95" t="s">
+        <v>266</v>
+      </c>
+      <c r="I5" s="95" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="6" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C6" s="87" t="s">
+        <v>249</v>
+      </c>
+      <c r="D6" s="88" t="s">
+        <v>281</v>
+      </c>
+      <c r="E6" s="88" t="s">
+        <v>280</v>
+      </c>
+      <c r="G6" s="87" t="s">
+        <v>249</v>
+      </c>
+      <c r="H6" s="88" t="s">
+        <v>281</v>
+      </c>
+      <c r="I6" s="88" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="7" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C7" s="87" t="s">
+        <v>249</v>
+      </c>
+      <c r="D7" s="88" t="s">
+        <v>281</v>
+      </c>
+      <c r="E7" s="88" t="s">
+        <v>282</v>
+      </c>
+      <c r="G7" s="87" t="s">
+        <v>249</v>
+      </c>
+      <c r="H7" s="88" t="s">
+        <v>281</v>
+      </c>
+      <c r="I7" s="88" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="8" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C8" s="82" t="s">
+        <v>271</v>
+      </c>
+      <c r="D8" s="83" t="s">
+        <v>254</v>
+      </c>
+      <c r="E8" s="83"/>
+      <c r="G8" s="94" t="s">
+        <v>272</v>
+      </c>
+      <c r="H8" s="95" t="s">
+        <v>281</v>
+      </c>
+      <c r="I8" s="95" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="90" t="s">
+        <v>272</v>
+      </c>
+      <c r="D9" s="91" t="s">
+        <v>281</v>
+      </c>
+      <c r="E9" s="91" t="s">
+        <v>225</v>
+      </c>
+      <c r="G9" s="87" t="s">
+        <v>343</v>
+      </c>
+      <c r="H9" s="88" t="s">
+        <v>281</v>
+      </c>
+      <c r="I9" s="88" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="10" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C10" s="89" t="s">
+        <v>272</v>
+      </c>
+      <c r="D10" s="86" t="s">
+        <v>281</v>
+      </c>
+      <c r="E10" s="86" t="s">
+        <v>251</v>
+      </c>
+      <c r="G10" s="87" t="s">
+        <v>343</v>
+      </c>
+      <c r="H10" s="88" t="s">
+        <v>281</v>
+      </c>
+      <c r="I10" s="88" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="11" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C11" s="87" t="s">
+        <v>272</v>
+      </c>
+      <c r="D11" s="88" t="s">
+        <v>281</v>
+      </c>
+      <c r="E11" s="88" t="s">
+        <v>283</v>
+      </c>
+      <c r="G11" s="80" t="s">
+        <v>385</v>
+      </c>
+      <c r="H11" s="81" t="s">
+        <v>248</v>
+      </c>
+      <c r="I11" s="81" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="12" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C12" s="87" t="s">
+        <v>272</v>
+      </c>
+      <c r="D12" s="88" t="s">
+        <v>281</v>
+      </c>
+      <c r="E12" s="88" t="s">
+        <v>284</v>
+      </c>
+      <c r="G12" s="89" t="s">
+        <v>263</v>
+      </c>
+      <c r="H12" s="86" t="s">
+        <v>281</v>
+      </c>
+      <c r="I12" s="86" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="13" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="80" t="s">
+        <v>268</v>
+      </c>
+      <c r="D13" s="81" t="s">
+        <v>252</v>
+      </c>
+      <c r="E13" s="81" t="s">
+        <v>253</v>
+      </c>
+      <c r="G13" s="90" t="s">
+        <v>263</v>
+      </c>
+      <c r="H13" s="91" t="s">
+        <v>281</v>
+      </c>
+      <c r="I13" s="91" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="14" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C14" s="87" t="s">
+        <v>258</v>
+      </c>
+      <c r="D14" s="88" t="s">
+        <v>281</v>
+      </c>
+      <c r="E14" s="88" t="s">
+        <v>285</v>
+      </c>
+      <c r="G14" s="87" t="s">
+        <v>263</v>
+      </c>
+      <c r="H14" s="88" t="s">
+        <v>281</v>
+      </c>
+      <c r="I14" s="88" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="15" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="87" t="s">
+        <v>258</v>
+      </c>
+      <c r="D15" s="88" t="s">
+        <v>281</v>
+      </c>
+      <c r="E15" s="88" t="s">
+        <v>286</v>
+      </c>
+      <c r="G15" s="87" t="s">
+        <v>263</v>
+      </c>
+      <c r="H15" s="88" t="s">
+        <v>281</v>
+      </c>
+      <c r="I15" s="88" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="16" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C16" s="90" t="s">
+        <v>258</v>
+      </c>
+      <c r="D16" s="91" t="s">
+        <v>281</v>
+      </c>
+      <c r="E16" s="91" t="s">
+        <v>225</v>
+      </c>
+      <c r="G16" s="125" t="s">
+        <v>362</v>
+      </c>
+      <c r="H16" s="83"/>
+      <c r="I16" s="83"/>
+    </row>
+    <row r="17" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C17" s="89" t="s">
+        <v>258</v>
+      </c>
+      <c r="D17" s="86" t="s">
+        <v>281</v>
+      </c>
+      <c r="E17" s="86" t="s">
+        <v>256</v>
+      </c>
+      <c r="G17" s="89" t="s">
+        <v>269</v>
+      </c>
+      <c r="H17" s="86" t="s">
+        <v>281</v>
+      </c>
+      <c r="I17" s="86" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="18" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C18" s="82" t="s">
+        <v>270</v>
+      </c>
+      <c r="D18" s="83" t="s">
+        <v>254</v>
+      </c>
+      <c r="E18" s="83"/>
+      <c r="G18" s="90" t="s">
+        <v>269</v>
+      </c>
+      <c r="H18" s="91" t="s">
+        <v>281</v>
+      </c>
+      <c r="I18" s="91" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="19" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C19" s="87" t="s">
+        <v>267</v>
+      </c>
+      <c r="D19" s="88" t="s">
+        <v>281</v>
+      </c>
+      <c r="E19" s="88" t="s">
+        <v>287</v>
+      </c>
+      <c r="G19" s="87" t="s">
+        <v>269</v>
+      </c>
+      <c r="H19" s="88" t="s">
+        <v>281</v>
+      </c>
+      <c r="I19" s="88" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="20" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C20" s="87" t="s">
+        <v>267</v>
+      </c>
+      <c r="D20" s="88" t="s">
+        <v>281</v>
+      </c>
+      <c r="E20" s="88" t="s">
+        <v>288</v>
+      </c>
+      <c r="G20" s="87" t="s">
+        <v>269</v>
+      </c>
+      <c r="H20" s="88" t="s">
+        <v>281</v>
+      </c>
+      <c r="I20" s="88" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="21" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C21" s="90" t="s">
+        <v>267</v>
+      </c>
+      <c r="D21" s="91" t="s">
+        <v>281</v>
+      </c>
+      <c r="E21" s="91" t="s">
+        <v>295</v>
+      </c>
+      <c r="G21" s="125" t="s">
+        <v>362</v>
+      </c>
+      <c r="H21" s="83"/>
+      <c r="I21" s="83"/>
+    </row>
+    <row r="22" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C22" s="89" t="s">
+        <v>267</v>
+      </c>
+      <c r="D22" s="86" t="s">
+        <v>281</v>
+      </c>
+      <c r="E22" s="86" t="s">
+        <v>262</v>
+      </c>
+      <c r="G22" s="89" t="s">
+        <v>346</v>
+      </c>
+      <c r="H22" s="86" t="s">
+        <v>281</v>
+      </c>
+      <c r="I22" s="86" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="23" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C23" s="82" t="s">
+        <v>289</v>
+      </c>
+      <c r="D23" s="83" t="s">
+        <v>254</v>
+      </c>
+      <c r="E23" s="83"/>
+      <c r="G23" s="90" t="s">
+        <v>346</v>
+      </c>
+      <c r="H23" s="91" t="s">
+        <v>281</v>
+      </c>
+      <c r="I23" s="91" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="24" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C24" s="87" t="s">
+        <v>290</v>
+      </c>
+      <c r="D24" s="88" t="s">
+        <v>281</v>
+      </c>
+      <c r="E24" s="88" t="s">
+        <v>291</v>
+      </c>
+      <c r="G24" s="87" t="s">
+        <v>346</v>
+      </c>
+      <c r="H24" s="88" t="s">
+        <v>281</v>
+      </c>
+      <c r="I24" s="88" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="25" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C25" s="87" t="s">
+        <v>290</v>
+      </c>
+      <c r="D25" s="88" t="s">
+        <v>281</v>
+      </c>
+      <c r="E25" s="88" t="s">
+        <v>292</v>
+      </c>
+      <c r="G25" s="87" t="s">
+        <v>346</v>
+      </c>
+      <c r="H25" s="88" t="s">
+        <v>281</v>
+      </c>
+      <c r="I25" s="88" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="26" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C26" s="94" t="s">
+        <v>290</v>
+      </c>
+      <c r="D26" s="95" t="s">
+        <v>281</v>
+      </c>
+      <c r="E26" s="95" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" s="84" t="s">
+        <v>347</v>
+      </c>
+      <c r="H26" s="85" t="s">
+        <v>281</v>
+      </c>
+      <c r="I26" s="85" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="27" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C27" s="84" t="s">
+        <v>298</v>
+      </c>
+      <c r="D27" s="85" t="s">
+        <v>297</v>
+      </c>
+      <c r="E27" s="85" t="s">
+        <v>275</v>
+      </c>
+      <c r="G27" s="74" t="s">
+        <v>359</v>
+      </c>
+      <c r="H27" s="75" t="s">
+        <v>248</v>
+      </c>
+      <c r="I27" s="75" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="28" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C28" s="74" t="s">
+        <v>296</v>
+      </c>
+      <c r="D28" s="75" t="s">
+        <v>248</v>
+      </c>
+      <c r="E28" s="75" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="29" spans="3:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C29" s="74" t="s">
+        <v>293</v>
+      </c>
+      <c r="D29" s="75" t="s">
+        <v>248</v>
+      </c>
+      <c r="E29" s="75" t="s">
+        <v>279</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C90927C-E429-4027-AD10-6911CE818B5A}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="C1:E24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="13.42578125" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" customWidth="1"/>
+    <col min="5" max="5" width="45.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="2" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="72" t="s">
+        <v>245</v>
+      </c>
+      <c r="D3" s="73" t="s">
+        <v>246</v>
+      </c>
+      <c r="E3" s="73" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="4" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="74" t="s">
+        <v>247</v>
+      </c>
+      <c r="D4" s="75" t="s">
+        <v>248</v>
+      </c>
+      <c r="E4" s="75" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="5" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C5" s="94" t="s">
+        <v>249</v>
+      </c>
+      <c r="D5" s="95" t="s">
+        <v>281</v>
+      </c>
+      <c r="E5" s="95" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="6" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C6" s="87" t="s">
+        <v>349</v>
+      </c>
+      <c r="D6" s="88" t="s">
+        <v>348</v>
+      </c>
+      <c r="E6" s="88" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="7" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C7" s="87" t="s">
+        <v>349</v>
+      </c>
+      <c r="D7" s="88" t="s">
+        <v>348</v>
+      </c>
+      <c r="E7" s="88" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="8" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C8" s="89" t="s">
+        <v>340</v>
+      </c>
+      <c r="D8" s="86" t="s">
+        <v>297</v>
+      </c>
+      <c r="E8" s="86" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="9" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="87" t="s">
+        <v>350</v>
+      </c>
+      <c r="D9" s="88" t="s">
+        <v>348</v>
+      </c>
+      <c r="E9" s="88" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="10" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C10" s="87" t="s">
+        <v>350</v>
+      </c>
+      <c r="D10" s="88" t="s">
+        <v>348</v>
+      </c>
+      <c r="E10" s="88" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="11" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C11" s="90" t="s">
+        <v>341</v>
+      </c>
+      <c r="D11" s="91" t="s">
+        <v>297</v>
+      </c>
+      <c r="E11" s="91" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="12" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C12" s="87" t="s">
+        <v>351</v>
+      </c>
+      <c r="D12" s="88" t="s">
+        <v>348</v>
+      </c>
+      <c r="E12" s="88" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="13" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="87" t="s">
+        <v>351</v>
+      </c>
+      <c r="D13" s="88" t="s">
+        <v>348</v>
+      </c>
+      <c r="E13" s="88" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="14" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C14" s="82" t="s">
+        <v>344</v>
+      </c>
+      <c r="D14" s="83" t="s">
+        <v>254</v>
+      </c>
+      <c r="E14" s="83"/>
+    </row>
+    <row r="15" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="80" t="s">
+        <v>258</v>
+      </c>
+      <c r="D15" s="81" t="s">
+        <v>252</v>
+      </c>
+      <c r="E15" s="81" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="16" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C16" s="82" t="s">
+        <v>345</v>
+      </c>
+      <c r="D16" s="83" t="s">
+        <v>254</v>
+      </c>
+      <c r="E16" s="83"/>
+    </row>
+    <row r="17" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C17" s="87" t="s">
+        <v>352</v>
+      </c>
+      <c r="D17" s="88" t="s">
+        <v>348</v>
+      </c>
+      <c r="E17" s="88" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="18" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C18" s="87" t="s">
+        <v>352</v>
+      </c>
+      <c r="D18" s="88" t="s">
+        <v>348</v>
+      </c>
+      <c r="E18" s="88" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="19" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C19" s="87" t="s">
+        <v>353</v>
+      </c>
+      <c r="D19" s="88" t="s">
+        <v>348</v>
+      </c>
+      <c r="E19" s="88" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="20" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C20" s="87" t="s">
+        <v>353</v>
+      </c>
+      <c r="D20" s="88" t="s">
+        <v>348</v>
+      </c>
+      <c r="E20" s="88" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="21" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C21" s="94" t="s">
+        <v>354</v>
+      </c>
+      <c r="D21" s="95" t="s">
+        <v>281</v>
+      </c>
+      <c r="E21" s="95" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C22" s="84" t="s">
+        <v>355</v>
+      </c>
+      <c r="D22" s="85" t="s">
+        <v>297</v>
+      </c>
+      <c r="E22" s="85" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="23" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C23" s="74" t="s">
+        <v>356</v>
+      </c>
+      <c r="D23" s="75" t="s">
+        <v>248</v>
+      </c>
+      <c r="E23" s="75" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="24" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C24" s="74" t="s">
+        <v>357</v>
+      </c>
+      <c r="D24" s="75" t="s">
+        <v>248</v>
+      </c>
+      <c r="E24" s="75" t="s">
+        <v>279</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C043FC81-2B1C-42A4-AF20-4408266546EE}">
+  <dimension ref="C1:E24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="13.42578125" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" customWidth="1"/>
+    <col min="5" max="5" width="45.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="2" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="72" t="s">
+        <v>245</v>
+      </c>
+      <c r="D3" s="73" t="s">
+        <v>246</v>
+      </c>
+      <c r="E3" s="73" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="4" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="74" t="s">
+        <v>247</v>
+      </c>
+      <c r="D4" s="75" t="s">
+        <v>248</v>
+      </c>
+      <c r="E4" s="75" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="5" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C5" s="87" t="s">
+        <v>249</v>
+      </c>
+      <c r="D5" s="88" t="s">
+        <v>252</v>
+      </c>
+      <c r="E5" s="88" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="6" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C6" s="90" t="s">
+        <v>249</v>
+      </c>
+      <c r="D6" s="91" t="s">
+        <v>252</v>
+      </c>
+      <c r="E6" s="91" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="7" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C7" s="89" t="s">
+        <v>249</v>
+      </c>
+      <c r="D7" s="86" t="s">
+        <v>252</v>
+      </c>
+      <c r="E7" s="86" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="8" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C8" s="76" t="s">
+        <v>294</v>
+      </c>
+      <c r="D8" s="77" t="s">
+        <v>266</v>
+      </c>
+      <c r="E8" s="77" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="9" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="78" t="s">
+        <v>273</v>
+      </c>
+      <c r="D9" s="79" t="s">
+        <v>254</v>
+      </c>
+      <c r="E9" s="79"/>
+    </row>
+    <row r="10" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C10" s="80" t="s">
+        <v>255</v>
+      </c>
+      <c r="D10" s="81" t="s">
+        <v>252</v>
+      </c>
+      <c r="E10" s="81" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="11" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C11" s="87" t="s">
+        <v>263</v>
+      </c>
+      <c r="D11" s="88" t="s">
+        <v>252</v>
+      </c>
+      <c r="E11" s="88" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="12" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C12" s="87" t="s">
+        <v>263</v>
+      </c>
+      <c r="D12" s="88" t="s">
+        <v>252</v>
+      </c>
+      <c r="E12" s="88" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="13" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="90" t="s">
+        <v>263</v>
+      </c>
+      <c r="D13" s="91" t="s">
+        <v>252</v>
+      </c>
+      <c r="E13" s="91" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="14" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C14" s="89" t="s">
+        <v>263</v>
+      </c>
+      <c r="D14" s="86" t="s">
+        <v>252</v>
+      </c>
+      <c r="E14" s="86" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="15" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="82" t="s">
+        <v>274</v>
+      </c>
+      <c r="D15" s="83" t="s">
+        <v>254</v>
+      </c>
+      <c r="E15" s="83"/>
+    </row>
+    <row r="16" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C16" s="87" t="s">
+        <v>269</v>
+      </c>
+      <c r="D16" s="88" t="s">
+        <v>252</v>
+      </c>
+      <c r="E16" s="88" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="17" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C17" s="87" t="s">
+        <v>269</v>
+      </c>
+      <c r="D17" s="88" t="s">
+        <v>252</v>
+      </c>
+      <c r="E17" s="88" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="18" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C18" s="90" t="s">
+        <v>269</v>
+      </c>
+      <c r="D18" s="91" t="s">
+        <v>252</v>
+      </c>
+      <c r="E18" s="91" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="19" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C19" s="89" t="s">
+        <v>269</v>
+      </c>
+      <c r="D19" s="86" t="s">
+        <v>252</v>
+      </c>
+      <c r="E19" s="86" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="20" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C20" s="82" t="s">
+        <v>270</v>
+      </c>
+      <c r="D20" s="83" t="s">
+        <v>254</v>
+      </c>
+      <c r="E20" s="83"/>
+    </row>
+    <row r="21" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C21" s="76" t="s">
+        <v>267</v>
+      </c>
+      <c r="D21" s="77" t="s">
+        <v>252</v>
+      </c>
+      <c r="E21" s="77" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C22" s="84" t="s">
+        <v>299</v>
+      </c>
+      <c r="D22" s="85" t="s">
+        <v>297</v>
+      </c>
+      <c r="E22" s="85" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="23" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C23" s="74" t="s">
+        <v>300</v>
+      </c>
+      <c r="D23" s="75" t="s">
+        <v>248</v>
+      </c>
+      <c r="E23" s="75" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="24" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C24" s="74" t="s">
+        <v>301</v>
+      </c>
+      <c r="D24" s="75" t="s">
+        <v>248</v>
+      </c>
+      <c r="E24" s="75" t="s">
+        <v>279</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CE7F58C-486E-43F9-844B-9308154A6A56}">
   <dimension ref="B1:H7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1440,5 +8344,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>